--- a/SIM_Data_Validation_DEMO.xlsx
+++ b/SIM_Data_Validation_DEMO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danut\AppData\Local\Temp\claude\simwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C72BC300-F7F6-48DB-9DA7-4D4B8F53A897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{875778E0-AF46-4703-A6D0-3873C1E541BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="1057">
   <si>
     <t>SIM data validation - working demo</t>
   </si>
@@ -2763,9 +2763,6 @@
     <t>+421912345678</t>
   </si>
   <si>
-    <t>WARNING: SIM_Country empty</t>
-  </si>
-  <si>
     <t>Sarah</t>
   </si>
   <si>
@@ -3097,6 +3094,147 @@
   </si>
   <si>
     <t>Country list: tblCountries on the Config sheet holds every ISO 3166-1 country and territory plus Kosovo (250 rows). SIM_Country has to match a Name there exactly, capitalisation aside. A country that is missing or misspelt turns the SIM_Country cell amber; one that only differs by stray spaces gets its own message in IsPhoneValid.</t>
+  </si>
+  <si>
+    <t>Data 10GB</t>
+  </si>
+  <si>
+    <t>Telekom</t>
+  </si>
+  <si>
+    <t>ana.popescu@example.com</t>
+  </si>
+  <si>
+    <t>Business M</t>
+  </si>
+  <si>
+    <t>Vodafone</t>
+  </si>
+  <si>
+    <t>mihai.ionescu@example.com</t>
+  </si>
+  <si>
+    <t>Business L</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>elena.dumitru@example.com</t>
+  </si>
+  <si>
+    <t>lukas.muller@example.com</t>
+  </si>
+  <si>
+    <t>claire.dubois@example.com</t>
+  </si>
+  <si>
+    <t>sven.jansen@example.com</t>
+  </si>
+  <si>
+    <t>marco.rossi@example.com</t>
+  </si>
+  <si>
+    <t>sofia.garcia@example.com</t>
+  </si>
+  <si>
+    <t>james.whitfield@example.com</t>
+  </si>
+  <si>
+    <t>piotr.kowalski@example.com</t>
+  </si>
+  <si>
+    <t>nadia.okonkwo@example.com</t>
+  </si>
+  <si>
+    <t>tomas.varga@example.com</t>
+  </si>
+  <si>
+    <t>sarah.bennett@example.com</t>
+  </si>
+  <si>
+    <t>kenji.tanaka@example.com</t>
+  </si>
+  <si>
+    <t>ingrid.larsen@example.com</t>
+  </si>
+  <si>
+    <t>petra.novak@example.com</t>
+  </si>
+  <si>
+    <t>ivan.petrov@example.com</t>
+  </si>
+  <si>
+    <t>anja.berg@example.com</t>
+  </si>
+  <si>
+    <t>rui.costa@example.com</t>
+  </si>
+  <si>
+    <t>katri.nieminen@example.com</t>
+  </si>
+  <si>
+    <t>bea.toth@example.com</t>
+  </si>
+  <si>
+    <t>omar.haddad@example.com</t>
+  </si>
+  <si>
+    <t>yara.levi@example.com</t>
+  </si>
+  <si>
+    <t>nils.eriksson@example.com</t>
+  </si>
+  <si>
+    <t>lena.fischer@example.com</t>
+  </si>
+  <si>
+    <t>hugo.silva@example.com</t>
+  </si>
+  <si>
+    <t>aoife.byrne@example.com</t>
+  </si>
+  <si>
+    <t>milan.horvat@example.com</t>
+  </si>
+  <si>
+    <t>eva.kovac@example.com</t>
+  </si>
+  <si>
+    <t>jonas.weber@example.com</t>
+  </si>
+  <si>
+    <t>marta.ruiz@example.com</t>
+  </si>
+  <si>
+    <t>finn.olsen@example.com</t>
+  </si>
+  <si>
+    <t>zoe.papadopoulos@example.com</t>
+  </si>
+  <si>
+    <t>viktor.sokolov@example.com</t>
+  </si>
+  <si>
+    <t>SIM_Country missing: required (red) - and the phone code cannot be checked (amber)</t>
+  </si>
+  <si>
+    <t>Irina</t>
+  </si>
+  <si>
+    <t>Required fields: PhoneNr, Plan, ICC_ID, SIM_Country, Provider and Email all missing</t>
+  </si>
+  <si>
+    <t>Required fields</t>
+  </si>
+  <si>
+    <t>PhoneNr, SIM_Country, Provider, Plan, ICC_ID and Email must be filled in on every row that is in use. A row is in use as soon as any input cell on it holds something; completely blank spare rows are ignored.</t>
+  </si>
+  <si>
+    <t>A missing required field is a RED error: the empty cell itself turns red, RowErrors lists it as "&lt;field&gt;: Required - this field is missing", and for PhoneNr and ICC_ID the same text appears in IsPhoneValid and ICC_Check.</t>
+  </si>
+  <si>
+    <t>A cell that holds only spaces counts as missing. Row 36 on the query sheet shows all six missing at once.</t>
   </si>
 </sst>
 </file>
@@ -3104,7 +3242,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -3197,15 +3335,84 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="38">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3450,33 +3657,6 @@
     <dxf>
       <font>
         <sz val="10"/>
-        <color rgb="FF006100"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
         <color rgb="FF9C5700"/>
         <name val="Arial"/>
       </font>
@@ -3484,6 +3664,18 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3569,54 +3761,13 @@
     </dxf>
     <dxf>
       <font>
-        <sz val="10"/>
-        <color rgb="FF006100"/>
-        <name val="Arial"/>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C5700"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C5700"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3662,83 +3813,18 @@
     </dxf>
     <dxf>
       <font>
-        <sz val="10"/>
-        <color rgb="FF006100"/>
-        <name val="Arial"/>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C5700"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF006100"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C5700"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3768,8 +3854,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_query" displayName="Table_query" ref="A1:AB35">
-  <autoFilter ref="A1:AB35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_query" displayName="Table_query" ref="A1:AB36">
+  <autoFilter ref="A1:AB36" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="FirstName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="LastName"/>
@@ -3791,14 +3877,14 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Email"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="ID"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="IsPhoneValid">
-      <calculatedColumnFormula>IF($C2="","",IF($V2="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V2,ROW(INDIRECT("1:"&amp;LEN($V2))),1)))=LEN($V2)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V2)&lt;8,"Too short - "&amp;LEN($V2)&amp;" digits (min 8)",IF(LEN($V2)&gt;15,"Too long - "&amp;LEN($V2)&amp;" digits (max 15)",IF($H2="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H2,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H2,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H2&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H2&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V2,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0")&amp;" for "&amp;$H2,"OK"))))))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF($C2="",IF(SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0,"Required - this field is missing",""),IF($V2="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V2,ROW(INDIRECT("1:"&amp;LEN($V2))),1)))=LEN($V2)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V2)&lt;8,"Too short - "&amp;LEN($V2)&amp;" digits (min 8)",IF(LEN($V2)&gt;15,"Too long - "&amp;LEN($V2)&amp;" digits (max 15)",IF($H2="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H2,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H2,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H2&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H2&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V2,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0")&amp;" for "&amp;$H2,"OK"))))))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="IMEI"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="PhoneClean" dataDxfId="0">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="PhoneClean" dataDxfId="37">
       <calculatedColumnFormula>IF($C2="","",IF(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C2&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),""),2)="00",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C2&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),""),3,255),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C2&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),"")))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="ICC_Check">
-      <calculatedColumnFormula>IF($E2="","",IF(ISNUMBER($E2),"Stored as a NUMBER - every digit past the 15th is already lost. Format the column as Text and re-enter.",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)))=LEN(TRIM($E2&amp;""))),"Digits only - no +, -, spaces or any other character",IF(LEFT(TRIM($E2&amp;""),2)&lt;&gt;"89","Must start with 89 (ITU-T E.118 telecom prefix)",IF(LEN(TRIM($E2&amp;""))&lt;18,"Too short - "&amp;LEN(TRIM($E2&amp;""))&amp;" digits (min 18)",IF(LEN(TRIM($E2&amp;""))&gt;22,"Too long - "&amp;LEN(TRIM($E2&amp;""))&amp;" digits (max 22)",IF(NOT(MOD(SUMPRODUCT(MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)*1*(1+MOD(LEN(TRIM($E2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),2))-MOD(LEN(TRIM($E2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),2)*9*(MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)*1*2&gt;9)),10)=0),"WARNING: Luhn check digit does not match - likely a typo or a transposition","OK")))))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF($E2="",IF(SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0,"Required - this field is missing",""),IF(ISNUMBER($E2),"Stored as a NUMBER - every digit past the 15th is already lost. Format the column as Text and re-enter.",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)))=LEN(TRIM($E2&amp;""))),"Digits only - no +, -, spaces or any other character",IF(LEFT(TRIM($E2&amp;""),2)&lt;&gt;"89","Must start with 89 (ITU-T E.118 telecom prefix)",IF(LEN(TRIM($E2&amp;""))&lt;18,"Too short - "&amp;LEN(TRIM($E2&amp;""))&amp;" digits (min 18)",IF(LEN(TRIM($E2&amp;""))&gt;22,"Too long - "&amp;LEN(TRIM($E2&amp;""))&amp;" digits (max 22)",IF(NOT(MOD(SUMPRODUCT(MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)*1*(1+MOD(LEN(TRIM($E2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),2))-MOD(LEN(TRIM($E2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),2)*9*(MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)*1*2&gt;9)),10)=0),"WARNING: Luhn check digit does not match - likely a typo or a transposition","OK")))))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="IMEI_Check">
       <calculatedColumnFormula>IF($U2="","",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID(TRIM($U2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($U2&amp;"")))),1)))=LEN(TRIM($U2&amp;""))),"Digits only - no +, -, spaces or any other character",IF(LEN(TRIM($U2&amp;""))&lt;&gt;15,"Must be exactly 15 digits - this one has "&amp;LEN(TRIM($U2&amp;"")),IF(NOT(MOD(SUMPRODUCT(MID(TRIM($U2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($U2&amp;"")))),1)*1*(1+MOD(LEN(TRIM($U2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($U2&amp;"")))),2))-MOD(LEN(TRIM($U2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($U2&amp;"")))),2)*9*(MID(TRIM($U2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($U2&amp;"")))),1)*1*2&gt;9)),10)=0),"WARNING: Luhn check digit does not match - likely a typo or a transposition","OK"))))</calculatedColumnFormula>
@@ -3813,7 +3899,7 @@
       <calculatedColumnFormula>IF($Q2="","",IF(SUMPRODUCT(--EXACT($Q2,Config!$H$2:$H$3))&gt;0,"OK",IF(NOT(ISNA(MATCH($Q2,Config!$H$2:$H$3,0))),"WARNING: wrong capitalisation - should be """&amp;INDEX(Config!$H$2:$H$3,MATCH($Q2,Config!$H$2:$H$3,0))&amp;""" exactly","Must be one of: eSIM, Physical SIM")))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0100-00001C000000}" name="RowErrors">
-      <calculatedColumnFormula>IF(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  ")="","OK",LEFT(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  "),LEN(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  "))-6))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  ")&amp;IF(AND(TRIM($H2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Email: Required - this field is missing  //  ","")="","OK",LEFT(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  ")&amp;IF(AND(TRIM($H2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Email: Required - this field is missing  //  ",""),LEN(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  ")&amp;IF(AND(TRIM($H2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Email: Required - this field is missing  //  ",""))-6))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4105,7 +4191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:B69"/>
+  <dimension ref="B1:B74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4247,7 +4333,7 @@
     </row>
     <row r="30" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.35">
@@ -4336,7 +4422,7 @@
     </row>
     <row r="49" spans="2:2" ht="50" x14ac:dyDescent="0.35">
       <c r="B49" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.35">
@@ -4402,32 +4488,52 @@
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="65" spans="2:2" ht="25" x14ac:dyDescent="0.35">
       <c r="B65" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="66" spans="2:2" ht="37.5" x14ac:dyDescent="0.35">
       <c r="B66" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="67" spans="2:2" ht="25" x14ac:dyDescent="0.35">
       <c r="B67" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B68" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="37.5" x14ac:dyDescent="0.35">
       <c r="B69" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B71" s="3" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" ht="25" x14ac:dyDescent="0.35">
+      <c r="B72" s="2" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" ht="25" x14ac:dyDescent="0.35">
+      <c r="B73" s="2" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" s="2" t="s">
+        <v>1056</v>
       </c>
     </row>
   </sheetData>
@@ -8895,7 +9001,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AD35"/>
+  <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -9019,7 +9125,9 @@
       <c r="C2" s="9" t="s">
         <v>843</v>
       </c>
-      <c r="D2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E2" s="9" t="s">
         <v>844</v>
       </c>
@@ -9030,7 +9138,9 @@
       <c r="H2" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="I2" s="6"/>
+      <c r="I2" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
@@ -9043,21 +9153,23 @@
       <c r="Q2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="6"/>
+      <c r="R2" s="6" t="s">
+        <v>1012</v>
+      </c>
       <c r="S2" s="6"/>
       <c r="T2" s="6" t="str">
-        <f ca="1">IF($C2="","",IF($V2="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V2,ROW(INDIRECT("1:"&amp;LEN($V2))),1)))=LEN($V2)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V2)&lt;8,"Too short - "&amp;LEN($V2)&amp;" digits (min 8)",IF(LEN($V2)&gt;15,"Too long - "&amp;LEN($V2)&amp;" digits (max 15)",IF($H2="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H2,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H2,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H2&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H2&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V2,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0")&amp;" for "&amp;$H2,"OK"))))))))</f>
+        <f ca="1">IF($C2="",IF(SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0,"Required - this field is missing",""),IF($V2="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V2,ROW(INDIRECT("1:"&amp;LEN($V2))),1)))=LEN($V2)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V2)&lt;8,"Too short - "&amp;LEN($V2)&amp;" digits (min 8)",IF(LEN($V2)&gt;15,"Too long - "&amp;LEN($V2)&amp;" digits (max 15)",IF($H2="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H2,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H2,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H2&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H2&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V2,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H2,tblCountries[Name],0)),"0")&amp;" for "&amp;$H2,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U2" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V2" s="11" t="str">
+      <c r="V2" s="6" t="str">
         <f t="shared" ref="V2:V35" si="0">IF($C2="","",IF(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C2&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),""),2)="00",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C2&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),""),3,255),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C2&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),"")))</f>
         <v>40712345678</v>
       </c>
       <c r="W2" s="6" t="str">
-        <f t="shared" ref="W2:W35" ca="1" si="1">IF($E2="","",IF(ISNUMBER($E2),"Stored as a NUMBER - every digit past the 15th is already lost. Format the column as Text and re-enter.",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)))=LEN(TRIM($E2&amp;""))),"Digits only - no +, -, spaces or any other character",IF(LEFT(TRIM($E2&amp;""),2)&lt;&gt;"89","Must start with 89 (ITU-T E.118 telecom prefix)",IF(LEN(TRIM($E2&amp;""))&lt;18,"Too short - "&amp;LEN(TRIM($E2&amp;""))&amp;" digits (min 18)",IF(LEN(TRIM($E2&amp;""))&gt;22,"Too long - "&amp;LEN(TRIM($E2&amp;""))&amp;" digits (max 22)",IF(NOT(MOD(SUMPRODUCT(MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)*1*(1+MOD(LEN(TRIM($E2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),2))-MOD(LEN(TRIM($E2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),2)*9*(MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)*1*2&gt;9)),10)=0),"WARNING: Luhn check digit does not match - likely a typo or a transposition","OK")))))))</f>
+        <f t="shared" ref="W2:W35" ca="1" si="1">IF($E2="",IF(SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0,"Required - this field is missing",""),IF(ISNUMBER($E2),"Stored as a NUMBER - every digit past the 15th is already lost. Format the column as Text and re-enter.",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)))=LEN(TRIM($E2&amp;""))),"Digits only - no +, -, spaces or any other character",IF(LEFT(TRIM($E2&amp;""),2)&lt;&gt;"89","Must start with 89 (ITU-T E.118 telecom prefix)",IF(LEN(TRIM($E2&amp;""))&lt;18,"Too short - "&amp;LEN(TRIM($E2&amp;""))&amp;" digits (min 18)",IF(LEN(TRIM($E2&amp;""))&gt;22,"Too long - "&amp;LEN(TRIM($E2&amp;""))&amp;" digits (max 22)",IF(NOT(MOD(SUMPRODUCT(MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)*1*(1+MOD(LEN(TRIM($E2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),2))-MOD(LEN(TRIM($E2&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),2)*9*(MID(TRIM($E2&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E2&amp;"")))),1)*1*2&gt;9)),10)=0),"WARNING: Luhn check digit does not match - likely a typo or a transposition","OK")))))))</f>
         <v>OK</v>
       </c>
       <c r="X2" s="6" t="str">
@@ -9077,7 +9189,7 @@
         <v>OK</v>
       </c>
       <c r="AB2" s="6" t="str">
-        <f t="shared" ref="AB2:AB35" ca="1" si="4">IF(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  ")="","OK",LEFT(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  "),LEN(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  "))-6))</f>
+        <f t="shared" ref="AB2:AB35" ca="1" si="4">IF(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  ")&amp;IF(AND(TRIM($H2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Email: Required - this field is missing  //  ","")="","OK",LEFT(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  ")&amp;IF(AND(TRIM($H2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Email: Required - this field is missing  //  ",""),LEN(IF(OR($T2="",$T2="OK"),"","PhoneNr: "&amp;$T2&amp;"  //  ")&amp;IF(OR($W2="",$W2="OK"),"","ICC_ID: "&amp;$W2&amp;"  //  ")&amp;IF(OR($Y2="",$Y2="OK"),"","StartDate: "&amp;$Y2&amp;"  //  ")&amp;IF(OR($Z2="",$Z2="OK"),"","Status: "&amp;$Z2&amp;"  //  ")&amp;IF(OR($AA2="",$AA2="OK"),"","SIM Type: "&amp;$AA2&amp;"  //  ")&amp;IF(OR($X2="",$X2="OK"),"","IMEI: "&amp;$X2&amp;"  //  ")&amp;IF(AND(TRIM($H2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0),"Email: Required - this field is missing  //  ",""))-6))</f>
         <v>OK</v>
       </c>
       <c r="AC2" s="6"/>
@@ -9095,7 +9207,9 @@
       <c r="C3" s="9" t="s">
         <v>850</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E3" s="9" t="s">
         <v>851</v>
       </c>
@@ -9106,7 +9220,9 @@
       <c r="H3" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -9119,16 +9235,18 @@
       <c r="Q3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R3" s="6"/>
+      <c r="R3" s="6" t="s">
+        <v>1015</v>
+      </c>
       <c r="S3" s="6"/>
       <c r="T3" s="6" t="str">
-        <f ca="1">IF($C3="","",IF($V3="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V3,ROW(INDIRECT("1:"&amp;LEN($V3))),1)))=LEN($V3)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V3)&lt;8,"Too short - "&amp;LEN($V3)&amp;" digits (min 8)",IF(LEN($V3)&gt;15,"Too long - "&amp;LEN($V3)&amp;" digits (max 15)",IF($H3="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H3,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H3,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H3&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H3&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V3,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H3,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H3,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H3,tblCountries[Name],0)),"0")&amp;" for "&amp;$H3,"OK"))))))))</f>
+        <f ca="1">IF($C3="",IF(SUMPRODUCT(LEN($A3:$S3))+LEN($U3)&gt;0,"Required - this field is missing",""),IF($V3="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V3,ROW(INDIRECT("1:"&amp;LEN($V3))),1)))=LEN($V3)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V3)&lt;8,"Too short - "&amp;LEN($V3)&amp;" digits (min 8)",IF(LEN($V3)&gt;15,"Too long - "&amp;LEN($V3)&amp;" digits (max 15)",IF($H3="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H3,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H3,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H3&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H3&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V3,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H3,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H3,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H3,tblCountries[Name],0)),"0")&amp;" for "&amp;$H3,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U3" s="9" t="s">
         <v>853</v>
       </c>
-      <c r="V3" s="11" t="str">
+      <c r="V3" s="6" t="str">
         <f t="shared" si="0"/>
         <v>40712345678</v>
       </c>
@@ -9171,7 +9289,9 @@
       <c r="C4" s="9" t="s">
         <v>857</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E4" s="9" t="s">
         <v>858</v>
       </c>
@@ -9182,7 +9302,9 @@
       <c r="H4" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -9195,16 +9317,18 @@
       <c r="Q4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R4" s="6"/>
+      <c r="R4" s="6" t="s">
+        <v>1018</v>
+      </c>
       <c r="S4" s="6"/>
       <c r="T4" s="6" t="str">
-        <f ca="1">IF($C4="","",IF($V4="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V4,ROW(INDIRECT("1:"&amp;LEN($V4))),1)))=LEN($V4)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V4)&lt;8,"Too short - "&amp;LEN($V4)&amp;" digits (min 8)",IF(LEN($V4)&gt;15,"Too long - "&amp;LEN($V4)&amp;" digits (max 15)",IF($H4="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H4,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H4,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H4&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H4&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V4,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H4,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H4,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H4,tblCountries[Name],0)),"0")&amp;" for "&amp;$H4,"OK"))))))))</f>
+        <f ca="1">IF($C4="",IF(SUMPRODUCT(LEN($A4:$S4))+LEN($U4)&gt;0,"Required - this field is missing",""),IF($V4="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V4,ROW(INDIRECT("1:"&amp;LEN($V4))),1)))=LEN($V4)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V4)&lt;8,"Too short - "&amp;LEN($V4)&amp;" digits (min 8)",IF(LEN($V4)&gt;15,"Too long - "&amp;LEN($V4)&amp;" digits (max 15)",IF($H4="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H4,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H4,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H4&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H4&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V4,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H4,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H4,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H4,tblCountries[Name],0)),"0")&amp;" for "&amp;$H4,"OK"))))))))</f>
         <v>Wrong country code - must start with +40 for Romania</v>
       </c>
       <c r="U4" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V4" s="11" t="str">
+      <c r="V4" s="6" t="str">
         <f t="shared" si="0"/>
         <v>0712345678</v>
       </c>
@@ -9247,7 +9371,9 @@
       <c r="C5" s="9" t="s">
         <v>863</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E5" s="9" t="s">
         <v>864</v>
       </c>
@@ -9258,7 +9384,9 @@
       <c r="H5" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="I5" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -9271,16 +9399,18 @@
       <c r="Q5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R5" s="6"/>
+      <c r="R5" s="6" t="s">
+        <v>1019</v>
+      </c>
       <c r="S5" s="6"/>
       <c r="T5" s="6" t="str">
-        <f ca="1">IF($C5="","",IF($V5="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V5,ROW(INDIRECT("1:"&amp;LEN($V5))),1)))=LEN($V5)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V5)&lt;8,"Too short - "&amp;LEN($V5)&amp;" digits (min 8)",IF(LEN($V5)&gt;15,"Too long - "&amp;LEN($V5)&amp;" digits (max 15)",IF($H5="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H5,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H5,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H5&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H5&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V5,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H5,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H5,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H5,tblCountries[Name],0)),"0")&amp;" for "&amp;$H5,"OK"))))))))</f>
+        <f ca="1">IF($C5="",IF(SUMPRODUCT(LEN($A5:$S5))+LEN($U5)&gt;0,"Required - this field is missing",""),IF($V5="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V5,ROW(INDIRECT("1:"&amp;LEN($V5))),1)))=LEN($V5)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V5)&lt;8,"Too short - "&amp;LEN($V5)&amp;" digits (min 8)",IF(LEN($V5)&gt;15,"Too long - "&amp;LEN($V5)&amp;" digits (max 15)",IF($H5="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H5,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H5,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H5&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H5&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V5,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H5,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H5,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H5,tblCountries[Name],0)),"0")&amp;" for "&amp;$H5,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U5" s="9" t="s">
         <v>853</v>
       </c>
-      <c r="V5" s="11" t="str">
+      <c r="V5" s="6" t="str">
         <f t="shared" si="0"/>
         <v>4915112345678</v>
       </c>
@@ -9323,7 +9453,9 @@
       <c r="C6" s="9" t="s">
         <v>869</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E6" s="9" t="s">
         <v>844</v>
       </c>
@@ -9334,7 +9466,9 @@
       <c r="H6" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="I6" s="6"/>
+      <c r="I6" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -9347,16 +9481,18 @@
       <c r="Q6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R6" s="6"/>
+      <c r="R6" s="6" t="s">
+        <v>1020</v>
+      </c>
       <c r="S6" s="6"/>
       <c r="T6" s="6" t="str">
-        <f ca="1">IF($C6="","",IF($V6="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V6,ROW(INDIRECT("1:"&amp;LEN($V6))),1)))=LEN($V6)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V6)&lt;8,"Too short - "&amp;LEN($V6)&amp;" digits (min 8)",IF(LEN($V6)&gt;15,"Too long - "&amp;LEN($V6)&amp;" digits (max 15)",IF($H6="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H6,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H6,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H6&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H6&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V6,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H6,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H6,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H6,tblCountries[Name],0)),"0")&amp;" for "&amp;$H6,"OK"))))))))</f>
+        <f ca="1">IF($C6="",IF(SUMPRODUCT(LEN($A6:$S6))+LEN($U6)&gt;0,"Required - this field is missing",""),IF($V6="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V6,ROW(INDIRECT("1:"&amp;LEN($V6))),1)))=LEN($V6)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V6)&lt;8,"Too short - "&amp;LEN($V6)&amp;" digits (min 8)",IF(LEN($V6)&gt;15,"Too long - "&amp;LEN($V6)&amp;" digits (max 15)",IF($H6="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H6,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H6,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H6&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H6&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V6,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H6,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H6,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H6,tblCountries[Name],0)),"0")&amp;" for "&amp;$H6,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U6" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V6" s="11" t="str">
+      <c r="V6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>33612345678</v>
       </c>
@@ -9399,7 +9535,9 @@
       <c r="C7" s="9" t="s">
         <v>874</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E7" s="9" t="s">
         <v>844</v>
       </c>
@@ -9410,7 +9548,9 @@
       <c r="H7" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="I7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
@@ -9423,16 +9563,18 @@
       <c r="Q7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R7" s="6"/>
+      <c r="R7" s="6" t="s">
+        <v>1021</v>
+      </c>
       <c r="S7" s="6"/>
       <c r="T7" s="6" t="str">
-        <f ca="1">IF($C7="","",IF($V7="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V7,ROW(INDIRECT("1:"&amp;LEN($V7))),1)))=LEN($V7)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V7)&lt;8,"Too short - "&amp;LEN($V7)&amp;" digits (min 8)",IF(LEN($V7)&gt;15,"Too long - "&amp;LEN($V7)&amp;" digits (max 15)",IF($H7="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H7,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H7,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H7&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H7&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V7,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H7,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H7,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H7,tblCountries[Name],0)),"0")&amp;" for "&amp;$H7,"OK"))))))))</f>
+        <f ca="1">IF($C7="",IF(SUMPRODUCT(LEN($A7:$S7))+LEN($U7)&gt;0,"Required - this field is missing",""),IF($V7="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V7,ROW(INDIRECT("1:"&amp;LEN($V7))),1)))=LEN($V7)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V7)&lt;8,"Too short - "&amp;LEN($V7)&amp;" digits (min 8)",IF(LEN($V7)&gt;15,"Too long - "&amp;LEN($V7)&amp;" digits (max 15)",IF($H7="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H7,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H7,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H7&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H7&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V7,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H7,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H7,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H7,tblCountries[Name],0)),"0")&amp;" for "&amp;$H7,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U7" s="9" t="s">
         <v>853</v>
       </c>
-      <c r="V7" s="11" t="str">
+      <c r="V7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>31612345678</v>
       </c>
@@ -9475,7 +9617,9 @@
       <c r="C8" s="9" t="s">
         <v>879</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E8" s="9" t="s">
         <v>844</v>
       </c>
@@ -9486,7 +9630,9 @@
       <c r="H8" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="I8" s="6"/>
+      <c r="I8" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -9499,16 +9645,18 @@
       <c r="Q8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R8" s="6"/>
+      <c r="R8" s="6" t="s">
+        <v>1022</v>
+      </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6" t="str">
-        <f ca="1">IF($C8="","",IF($V8="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V8,ROW(INDIRECT("1:"&amp;LEN($V8))),1)))=LEN($V8)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V8)&lt;8,"Too short - "&amp;LEN($V8)&amp;" digits (min 8)",IF(LEN($V8)&gt;15,"Too long - "&amp;LEN($V8)&amp;" digits (max 15)",IF($H8="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H8,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H8,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H8&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H8&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V8,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H8,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H8,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H8,tblCountries[Name],0)),"0")&amp;" for "&amp;$H8,"OK"))))))))</f>
+        <f ca="1">IF($C8="",IF(SUMPRODUCT(LEN($A8:$S8))+LEN($U8)&gt;0,"Required - this field is missing",""),IF($V8="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V8,ROW(INDIRECT("1:"&amp;LEN($V8))),1)))=LEN($V8)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V8)&lt;8,"Too short - "&amp;LEN($V8)&amp;" digits (min 8)",IF(LEN($V8)&gt;15,"Too long - "&amp;LEN($V8)&amp;" digits (max 15)",IF($H8="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H8,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H8,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H8&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H8&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V8,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H8,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H8,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H8,tblCountries[Name],0)),"0")&amp;" for "&amp;$H8,"OK"))))))))</f>
         <v>Too short - 5 digits (min 8)</v>
       </c>
       <c r="U8" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V8" s="11" t="str">
+      <c r="V8" s="6" t="str">
         <f t="shared" si="0"/>
         <v>39123</v>
       </c>
@@ -9551,7 +9699,9 @@
       <c r="C9" s="9" t="s">
         <v>883</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E9" s="9" t="s">
         <v>844</v>
       </c>
@@ -9562,7 +9712,9 @@
       <c r="H9" s="6" t="s">
         <v>696</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="I9" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -9575,16 +9727,18 @@
       <c r="Q9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R9" s="6"/>
+      <c r="R9" s="6" t="s">
+        <v>1023</v>
+      </c>
       <c r="S9" s="6"/>
       <c r="T9" s="6" t="str">
-        <f ca="1">IF($C9="","",IF($V9="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V9,ROW(INDIRECT("1:"&amp;LEN($V9))),1)))=LEN($V9)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V9)&lt;8,"Too short - "&amp;LEN($V9)&amp;" digits (min 8)",IF(LEN($V9)&gt;15,"Too long - "&amp;LEN($V9)&amp;" digits (max 15)",IF($H9="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H9,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H9,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H9&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H9&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V9,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H9,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H9,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H9,tblCountries[Name],0)),"0")&amp;" for "&amp;$H9,"OK"))))))))</f>
+        <f ca="1">IF($C9="",IF(SUMPRODUCT(LEN($A9:$S9))+LEN($U9)&gt;0,"Required - this field is missing",""),IF($V9="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V9,ROW(INDIRECT("1:"&amp;LEN($V9))),1)))=LEN($V9)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V9)&lt;8,"Too short - "&amp;LEN($V9)&amp;" digits (min 8)",IF(LEN($V9)&gt;15,"Too long - "&amp;LEN($V9)&amp;" digits (max 15)",IF($H9="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H9,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H9,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H9&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H9&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V9,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H9,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H9,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H9,tblCountries[Name],0)),"0")&amp;" for "&amp;$H9,"OK"))))))))</f>
         <v>Too long - 17 digits (max 15)</v>
       </c>
       <c r="U9" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V9" s="11" t="str">
+      <c r="V9" s="6" t="str">
         <f t="shared" si="0"/>
         <v>34123456789012345</v>
       </c>
@@ -9627,7 +9781,9 @@
       <c r="C10" s="9" t="s">
         <v>887</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E10" s="9" t="s">
         <v>844</v>
       </c>
@@ -9638,7 +9794,9 @@
       <c r="H10" s="6" t="s">
         <v>771</v>
       </c>
-      <c r="I10" s="6"/>
+      <c r="I10" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
@@ -9651,16 +9809,18 @@
       <c r="Q10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R10" s="6"/>
+      <c r="R10" s="6" t="s">
+        <v>1024</v>
+      </c>
       <c r="S10" s="6"/>
       <c r="T10" s="6" t="str">
-        <f ca="1">IF($C10="","",IF($V10="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V10,ROW(INDIRECT("1:"&amp;LEN($V10))),1)))=LEN($V10)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V10)&lt;8,"Too short - "&amp;LEN($V10)&amp;" digits (min 8)",IF(LEN($V10)&gt;15,"Too long - "&amp;LEN($V10)&amp;" digits (max 15)",IF($H10="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H10,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H10,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H10&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H10&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V10,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H10,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H10,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H10,tblCountries[Name],0)),"0")&amp;" for "&amp;$H10,"OK"))))))))</f>
+        <f ca="1">IF($C10="",IF(SUMPRODUCT(LEN($A10:$S10))+LEN($U10)&gt;0,"Required - this field is missing",""),IF($V10="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V10,ROW(INDIRECT("1:"&amp;LEN($V10))),1)))=LEN($V10)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V10)&lt;8,"Too short - "&amp;LEN($V10)&amp;" digits (min 8)",IF(LEN($V10)&gt;15,"Too long - "&amp;LEN($V10)&amp;" digits (max 15)",IF($H10="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H10,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H10,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H10&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H10&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V10,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H10,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H10,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H10,tblCountries[Name],0)),"0")&amp;" for "&amp;$H10,"OK"))))))))</f>
         <v>Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)</v>
       </c>
       <c r="U10" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V10" s="11" t="str">
+      <c r="V10" s="6" t="str">
         <f t="shared" si="0"/>
         <v>44ABC12345</v>
       </c>
@@ -9703,7 +9863,9 @@
       <c r="C11" s="9" t="s">
         <v>843</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E11" s="9" t="s">
         <v>844</v>
       </c>
@@ -9714,7 +9876,9 @@
       <c r="H11" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
@@ -9727,16 +9891,18 @@
       <c r="Q11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R11" s="6"/>
+      <c r="R11" s="6" t="s">
+        <v>1025</v>
+      </c>
       <c r="S11" s="6"/>
       <c r="T11" s="6" t="str">
-        <f ca="1">IF($C11="","",IF($V11="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V11,ROW(INDIRECT("1:"&amp;LEN($V11))),1)))=LEN($V11)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V11)&lt;8,"Too short - "&amp;LEN($V11)&amp;" digits (min 8)",IF(LEN($V11)&gt;15,"Too long - "&amp;LEN($V11)&amp;" digits (max 15)",IF($H11="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H11,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H11,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H11&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H11&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V11,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H11,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H11,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H11,tblCountries[Name],0)),"0")&amp;" for "&amp;$H11,"OK"))))))))</f>
+        <f ca="1">IF($C11="",IF(SUMPRODUCT(LEN($A11:$S11))+LEN($U11)&gt;0,"Required - this field is missing",""),IF($V11="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V11,ROW(INDIRECT("1:"&amp;LEN($V11))),1)))=LEN($V11)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V11)&lt;8,"Too short - "&amp;LEN($V11)&amp;" digits (min 8)",IF(LEN($V11)&gt;15,"Too long - "&amp;LEN($V11)&amp;" digits (max 15)",IF($H11="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H11,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H11,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H11&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H11&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V11,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H11,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H11,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H11,tblCountries[Name],0)),"0")&amp;" for "&amp;$H11,"OK"))))))))</f>
         <v>Wrong country code - must start with +48 for Poland</v>
       </c>
       <c r="U11" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V11" s="11" t="str">
+      <c r="V11" s="6" t="str">
         <f t="shared" si="0"/>
         <v>40712345678</v>
       </c>
@@ -9779,7 +9945,9 @@
       <c r="C12" s="9" t="s">
         <v>843</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E12" s="9" t="s">
         <v>844</v>
       </c>
@@ -9790,7 +9958,9 @@
       <c r="H12" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="I12" s="6"/>
+      <c r="I12" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
@@ -9803,16 +9973,18 @@
       <c r="Q12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R12" s="6"/>
+      <c r="R12" s="6" t="s">
+        <v>1026</v>
+      </c>
       <c r="S12" s="6"/>
       <c r="T12" s="6" t="str">
-        <f ca="1">IF($C12="","",IF($V12="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V12,ROW(INDIRECT("1:"&amp;LEN($V12))),1)))=LEN($V12)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V12)&lt;8,"Too short - "&amp;LEN($V12)&amp;" digits (min 8)",IF(LEN($V12)&gt;15,"Too long - "&amp;LEN($V12)&amp;" digits (max 15)",IF($H12="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H12,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H12,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H12&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H12&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V12,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H12,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H12,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H12,tblCountries[Name],0)),"0")&amp;" for "&amp;$H12,"OK"))))))))</f>
+        <f ca="1">IF($C12="",IF(SUMPRODUCT(LEN($A12:$S12))+LEN($U12)&gt;0,"Required - this field is missing",""),IF($V12="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V12,ROW(INDIRECT("1:"&amp;LEN($V12))),1)))=LEN($V12)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V12)&lt;8,"Too short - "&amp;LEN($V12)&amp;" digits (min 8)",IF(LEN($V12)&gt;15,"Too long - "&amp;LEN($V12)&amp;" digits (max 15)",IF($H12="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H12,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H12,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H12&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H12&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V12,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H12,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H12,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H12,tblCountries[Name],0)),"0")&amp;" for "&amp;$H12,"OK"))))))))</f>
         <v>WARNING: SIM_Country "Wakanda" is not in tblCountries</v>
       </c>
       <c r="U12" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V12" s="11" t="str">
+      <c r="V12" s="6" t="str">
         <f t="shared" si="0"/>
         <v>40712345678</v>
       </c>
@@ -9855,7 +10027,9 @@
       <c r="C13" s="9" t="s">
         <v>898</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E13" s="9" t="s">
         <v>844</v>
       </c>
@@ -9864,7 +10038,9 @@
         <v>845</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
@@ -9877,16 +10053,18 @@
       <c r="Q13" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R13" s="6"/>
+      <c r="R13" s="6" t="s">
+        <v>1027</v>
+      </c>
       <c r="S13" s="6"/>
       <c r="T13" s="6" t="str">
-        <f ca="1">IF($C13="","",IF($V13="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V13,ROW(INDIRECT("1:"&amp;LEN($V13))),1)))=LEN($V13)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V13)&lt;8,"Too short - "&amp;LEN($V13)&amp;" digits (min 8)",IF(LEN($V13)&gt;15,"Too long - "&amp;LEN($V13)&amp;" digits (max 15)",IF($H13="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H13,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H13,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H13&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H13&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V13,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H13,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H13,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H13,tblCountries[Name],0)),"0")&amp;" for "&amp;$H13,"OK"))))))))</f>
+        <f ca="1">IF($C13="",IF(SUMPRODUCT(LEN($A13:$S13))+LEN($U13)&gt;0,"Required - this field is missing",""),IF($V13="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V13,ROW(INDIRECT("1:"&amp;LEN($V13))),1)))=LEN($V13)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V13)&lt;8,"Too short - "&amp;LEN($V13)&amp;" digits (min 8)",IF(LEN($V13)&gt;15,"Too long - "&amp;LEN($V13)&amp;" digits (max 15)",IF($H13="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H13,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H13,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H13&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H13&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V13,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H13,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H13,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H13,tblCountries[Name],0)),"0")&amp;" for "&amp;$H13,"OK"))))))))</f>
         <v>WARNING: SIM_Country is empty - cannot check the country code</v>
       </c>
       <c r="U13" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V13" s="11" t="str">
+      <c r="V13" s="6" t="str">
         <f t="shared" si="0"/>
         <v>421912345678</v>
       </c>
@@ -9912,24 +10090,26 @@
       </c>
       <c r="AB13" s="6" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>PhoneNr: WARNING: SIM_Country is empty - cannot check the country code</v>
+        <v>PhoneNr: WARNING: SIM_Country is empty - cannot check the country code  //  SIM_Country: Required - this field is missing</v>
       </c>
       <c r="AC13" s="6"/>
       <c r="AD13" s="7" t="s">
-        <v>899</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="9" t="s">
         <v>901</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>902</v>
-      </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E14" s="9" t="s">
         <v>844</v>
       </c>
@@ -9940,7 +10120,9 @@
       <c r="H14" s="6" t="s">
         <v>774</v>
       </c>
-      <c r="I14" s="6"/>
+      <c r="I14" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
@@ -9953,16 +10135,18 @@
       <c r="Q14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R14" s="6"/>
+      <c r="R14" s="6" t="s">
+        <v>1028</v>
+      </c>
       <c r="S14" s="6"/>
       <c r="T14" s="6" t="str">
-        <f ca="1">IF($C14="","",IF($V14="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V14,ROW(INDIRECT("1:"&amp;LEN($V14))),1)))=LEN($V14)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V14)&lt;8,"Too short - "&amp;LEN($V14)&amp;" digits (min 8)",IF(LEN($V14)&gt;15,"Too long - "&amp;LEN($V14)&amp;" digits (max 15)",IF($H14="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H14,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H14,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H14&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H14&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V14,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H14,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H14,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H14,tblCountries[Name],0)),"0")&amp;" for "&amp;$H14,"OK"))))))))</f>
+        <f ca="1">IF($C14="",IF(SUMPRODUCT(LEN($A14:$S14))+LEN($U14)&gt;0,"Required - this field is missing",""),IF($V14="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V14,ROW(INDIRECT("1:"&amp;LEN($V14))),1)))=LEN($V14)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V14)&lt;8,"Too short - "&amp;LEN($V14)&amp;" digits (min 8)",IF(LEN($V14)&gt;15,"Too long - "&amp;LEN($V14)&amp;" digits (max 15)",IF($H14="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H14,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H14,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H14&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H14&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V14,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H14,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H14,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H14,tblCountries[Name],0)),"0")&amp;" for "&amp;$H14,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U14" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V14" s="11" t="str">
+      <c r="V14" s="6" t="str">
         <f t="shared" si="0"/>
         <v>12025550143</v>
       </c>
@@ -9992,20 +10176,22 @@
       </c>
       <c r="AC14" s="6"/>
       <c r="AD14" s="7" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>904</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="9" t="s">
         <v>905</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>906</v>
-      </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E15" s="9" t="s">
         <v>844</v>
       </c>
@@ -10016,7 +10202,9 @@
       <c r="H15" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="I15" s="6"/>
+      <c r="I15" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
@@ -10029,16 +10217,18 @@
       <c r="Q15" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R15" s="6"/>
+      <c r="R15" s="6" t="s">
+        <v>1029</v>
+      </c>
       <c r="S15" s="6"/>
       <c r="T15" s="6" t="str">
-        <f ca="1">IF($C15="","",IF($V15="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V15,ROW(INDIRECT("1:"&amp;LEN($V15))),1)))=LEN($V15)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V15)&lt;8,"Too short - "&amp;LEN($V15)&amp;" digits (min 8)",IF(LEN($V15)&gt;15,"Too long - "&amp;LEN($V15)&amp;" digits (max 15)",IF($H15="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H15,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H15,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H15&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H15&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V15,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H15,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H15,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H15,tblCountries[Name],0)),"0")&amp;" for "&amp;$H15,"OK"))))))))</f>
+        <f ca="1">IF($C15="",IF(SUMPRODUCT(LEN($A15:$S15))+LEN($U15)&gt;0,"Required - this field is missing",""),IF($V15="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V15,ROW(INDIRECT("1:"&amp;LEN($V15))),1)))=LEN($V15)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V15)&lt;8,"Too short - "&amp;LEN($V15)&amp;" digits (min 8)",IF(LEN($V15)&gt;15,"Too long - "&amp;LEN($V15)&amp;" digits (max 15)",IF($H15="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H15,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H15,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H15&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H15&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V15,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H15,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H15,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H15,tblCountries[Name],0)),"0")&amp;" for "&amp;$H15,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U15" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V15" s="11" t="str">
+      <c r="V15" s="6" t="str">
         <f t="shared" si="0"/>
         <v>819012345678</v>
       </c>
@@ -10068,20 +10258,22 @@
       </c>
       <c r="AC15" s="6"/>
       <c r="AD15" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="9" t="s">
         <v>909</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>910</v>
-      </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E16" s="9" t="s">
         <v>844</v>
       </c>
@@ -10092,7 +10284,9 @@
       <c r="H16" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="I16" s="6"/>
+      <c r="I16" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
@@ -10105,16 +10299,18 @@
       <c r="Q16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R16" s="6"/>
+      <c r="R16" s="6" t="s">
+        <v>1030</v>
+      </c>
       <c r="S16" s="6"/>
       <c r="T16" s="6" t="str">
-        <f ca="1">IF($C16="","",IF($V16="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V16,ROW(INDIRECT("1:"&amp;LEN($V16))),1)))=LEN($V16)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V16)&lt;8,"Too short - "&amp;LEN($V16)&amp;" digits (min 8)",IF(LEN($V16)&gt;15,"Too long - "&amp;LEN($V16)&amp;" digits (max 15)",IF($H16="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H16,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H16,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H16&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H16&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V16,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H16,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H16,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H16,tblCountries[Name],0)),"0")&amp;" for "&amp;$H16,"OK"))))))))</f>
+        <f ca="1">IF($C16="",IF(SUMPRODUCT(LEN($A16:$S16))+LEN($U16)&gt;0,"Required - this field is missing",""),IF($V16="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V16,ROW(INDIRECT("1:"&amp;LEN($V16))),1)))=LEN($V16)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V16)&lt;8,"Too short - "&amp;LEN($V16)&amp;" digits (min 8)",IF(LEN($V16)&gt;15,"Too long - "&amp;LEN($V16)&amp;" digits (max 15)",IF($H16="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H16,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H16,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H16&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H16&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V16,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H16,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H16,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H16,tblCountries[Name],0)),"0")&amp;" for "&amp;$H16,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U16" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V16" s="11" t="str">
+      <c r="V16" s="6" t="str">
         <f t="shared" si="0"/>
         <v>4791234567</v>
       </c>
@@ -10149,17 +10345,19 @@
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="6" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>913</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="9" t="s">
-        <v>914</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="9" t="s">
@@ -10168,7 +10366,9 @@
       <c r="H17" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="I17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
@@ -10181,16 +10381,18 @@
       <c r="Q17" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R17" s="6"/>
+      <c r="R17" s="6" t="s">
+        <v>1031</v>
+      </c>
       <c r="S17" s="6"/>
       <c r="T17" s="6" t="str">
-        <f ca="1">IF($C17="","",IF($V17="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V17,ROW(INDIRECT("1:"&amp;LEN($V17))),1)))=LEN($V17)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V17)&lt;8,"Too short - "&amp;LEN($V17)&amp;" digits (min 8)",IF(LEN($V17)&gt;15,"Too long - "&amp;LEN($V17)&amp;" digits (max 15)",IF($H17="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H17,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H17,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H17&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H17&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V17,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H17,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H17,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H17,tblCountries[Name],0)),"0")&amp;" for "&amp;$H17,"OK"))))))))</f>
+        <f ca="1">IF($C17="",IF(SUMPRODUCT(LEN($A17:$S17))+LEN($U17)&gt;0,"Required - this field is missing",""),IF($V17="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V17,ROW(INDIRECT("1:"&amp;LEN($V17))),1)))=LEN($V17)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V17)&lt;8,"Too short - "&amp;LEN($V17)&amp;" digits (min 8)",IF(LEN($V17)&gt;15,"Too long - "&amp;LEN($V17)&amp;" digits (max 15)",IF($H17="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H17,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H17,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H17&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H17&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V17,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H17,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H17,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H17,tblCountries[Name],0)),"0")&amp;" for "&amp;$H17,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U17" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V17" s="11" t="str">
+      <c r="V17" s="6" t="str">
         <f t="shared" si="0"/>
         <v>420601234567</v>
       </c>
@@ -10220,22 +10422,24 @@
       </c>
       <c r="AC17" s="6"/>
       <c r="AD17" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="9" t="s">
         <v>917</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>918</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="9" t="s">
-        <v>919</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="9" t="s">
@@ -10244,7 +10448,9 @@
       <c r="H18" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="I18" s="6"/>
+      <c r="I18" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
@@ -10257,16 +10463,18 @@
       <c r="Q18" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R18" s="6"/>
+      <c r="R18" s="6" t="s">
+        <v>1032</v>
+      </c>
       <c r="S18" s="6"/>
       <c r="T18" s="6" t="str">
-        <f ca="1">IF($C18="","",IF($V18="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V18,ROW(INDIRECT("1:"&amp;LEN($V18))),1)))=LEN($V18)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V18)&lt;8,"Too short - "&amp;LEN($V18)&amp;" digits (min 8)",IF(LEN($V18)&gt;15,"Too long - "&amp;LEN($V18)&amp;" digits (max 15)",IF($H18="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H18,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H18,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H18&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H18&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V18,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H18,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H18,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H18,tblCountries[Name],0)),"0")&amp;" for "&amp;$H18,"OK"))))))))</f>
+        <f ca="1">IF($C18="",IF(SUMPRODUCT(LEN($A18:$S18))+LEN($U18)&gt;0,"Required - this field is missing",""),IF($V18="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V18,ROW(INDIRECT("1:"&amp;LEN($V18))),1)))=LEN($V18)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V18)&lt;8,"Too short - "&amp;LEN($V18)&amp;" digits (min 8)",IF(LEN($V18)&gt;15,"Too long - "&amp;LEN($V18)&amp;" digits (max 15)",IF($H18="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H18,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H18,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H18&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H18&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V18,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H18,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H18,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H18,tblCountries[Name],0)),"0")&amp;" for "&amp;$H18,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U18" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V18" s="11" t="str">
+      <c r="V18" s="6" t="str">
         <f t="shared" si="0"/>
         <v>359881234567</v>
       </c>
@@ -10296,22 +10504,24 @@
       </c>
       <c r="AC18" s="6"/>
       <c r="AD18" s="7" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>921</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="9" t="s">
         <v>922</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="D19" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>923</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="9" t="s">
-        <v>924</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="9" t="s">
@@ -10320,7 +10530,9 @@
       <c r="H19" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="I19" s="6"/>
+      <c r="I19" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
@@ -10333,16 +10545,18 @@
       <c r="Q19" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R19" s="6"/>
+      <c r="R19" s="6" t="s">
+        <v>1033</v>
+      </c>
       <c r="S19" s="6"/>
       <c r="T19" s="6" t="str">
-        <f ca="1">IF($C19="","",IF($V19="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V19,ROW(INDIRECT("1:"&amp;LEN($V19))),1)))=LEN($V19)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V19)&lt;8,"Too short - "&amp;LEN($V19)&amp;" digits (min 8)",IF(LEN($V19)&gt;15,"Too long - "&amp;LEN($V19)&amp;" digits (max 15)",IF($H19="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H19,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H19,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H19&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H19&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V19,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H19,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H19,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H19,tblCountries[Name],0)),"0")&amp;" for "&amp;$H19,"OK"))))))))</f>
+        <f ca="1">IF($C19="",IF(SUMPRODUCT(LEN($A19:$S19))+LEN($U19)&gt;0,"Required - this field is missing",""),IF($V19="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V19,ROW(INDIRECT("1:"&amp;LEN($V19))),1)))=LEN($V19)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V19)&lt;8,"Too short - "&amp;LEN($V19)&amp;" digits (min 8)",IF(LEN($V19)&gt;15,"Too long - "&amp;LEN($V19)&amp;" digits (max 15)",IF($H19="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H19,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H19,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H19&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H19&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V19,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H19,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H19,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H19,tblCountries[Name],0)),"0")&amp;" for "&amp;$H19,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U19" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V19" s="11" t="str">
+      <c r="V19" s="6" t="str">
         <f t="shared" si="0"/>
         <v>4791234567</v>
       </c>
@@ -10372,22 +10586,24 @@
       </c>
       <c r="AC19" s="6"/>
       <c r="AD19" s="7" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>926</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="9" t="s">
         <v>927</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="D20" s="6" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>928</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="9" t="s">
-        <v>929</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="9" t="s">
@@ -10396,7 +10612,9 @@
       <c r="H20" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="I20" s="6"/>
+      <c r="I20" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
@@ -10409,16 +10627,18 @@
       <c r="Q20" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R20" s="6"/>
+      <c r="R20" s="6" t="s">
+        <v>1034</v>
+      </c>
       <c r="S20" s="6"/>
       <c r="T20" s="6" t="str">
-        <f ca="1">IF($C20="","",IF($V20="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V20,ROW(INDIRECT("1:"&amp;LEN($V20))),1)))=LEN($V20)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V20)&lt;8,"Too short - "&amp;LEN($V20)&amp;" digits (min 8)",IF(LEN($V20)&gt;15,"Too long - "&amp;LEN($V20)&amp;" digits (max 15)",IF($H20="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H20,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H20,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H20&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H20&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V20,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H20,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H20,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H20,tblCountries[Name],0)),"0")&amp;" for "&amp;$H20,"OK"))))))))</f>
+        <f ca="1">IF($C20="",IF(SUMPRODUCT(LEN($A20:$S20))+LEN($U20)&gt;0,"Required - this field is missing",""),IF($V20="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V20,ROW(INDIRECT("1:"&amp;LEN($V20))),1)))=LEN($V20)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V20)&lt;8,"Too short - "&amp;LEN($V20)&amp;" digits (min 8)",IF(LEN($V20)&gt;15,"Too long - "&amp;LEN($V20)&amp;" digits (max 15)",IF($H20="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H20,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H20,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H20&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H20&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V20,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H20,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H20,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H20,tblCountries[Name],0)),"0")&amp;" for "&amp;$H20,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U20" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V20" s="11" t="str">
+      <c r="V20" s="6" t="str">
         <f t="shared" si="0"/>
         <v>351912345678</v>
       </c>
@@ -10448,22 +10668,24 @@
       </c>
       <c r="AC20" s="6"/>
       <c r="AD20" s="7" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="9" t="s">
         <v>932</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>933</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="9" t="s">
-        <v>934</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="9" t="s">
@@ -10472,7 +10694,9 @@
       <c r="H21" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="I21" s="6"/>
+      <c r="I21" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
@@ -10485,16 +10709,18 @@
       <c r="Q21" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R21" s="6"/>
+      <c r="R21" s="6" t="s">
+        <v>1035</v>
+      </c>
       <c r="S21" s="6"/>
       <c r="T21" s="6" t="str">
-        <f ca="1">IF($C21="","",IF($V21="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V21,ROW(INDIRECT("1:"&amp;LEN($V21))),1)))=LEN($V21)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V21)&lt;8,"Too short - "&amp;LEN($V21)&amp;" digits (min 8)",IF(LEN($V21)&gt;15,"Too long - "&amp;LEN($V21)&amp;" digits (max 15)",IF($H21="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H21,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H21,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H21&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H21&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V21,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H21,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H21,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H21,tblCountries[Name],0)),"0")&amp;" for "&amp;$H21,"OK"))))))))</f>
+        <f ca="1">IF($C21="",IF(SUMPRODUCT(LEN($A21:$S21))+LEN($U21)&gt;0,"Required - this field is missing",""),IF($V21="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V21,ROW(INDIRECT("1:"&amp;LEN($V21))),1)))=LEN($V21)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V21)&lt;8,"Too short - "&amp;LEN($V21)&amp;" digits (min 8)",IF(LEN($V21)&gt;15,"Too long - "&amp;LEN($V21)&amp;" digits (max 15)",IF($H21="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H21,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H21,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H21&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H21&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V21,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H21,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H21,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H21,tblCountries[Name],0)),"0")&amp;" for "&amp;$H21,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U21" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V21" s="11" t="str">
+      <c r="V21" s="6" t="str">
         <f t="shared" si="0"/>
         <v>358401234567</v>
       </c>
@@ -10524,20 +10750,22 @@
       </c>
       <c r="AC21" s="6"/>
       <c r="AD21" s="7" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="9" t="s">
         <v>937</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="D22" s="6"/>
+      <c r="D22" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E22" s="9" t="s">
         <v>864</v>
       </c>
@@ -10548,7 +10776,9 @@
       <c r="H22" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="I22" s="6"/>
+      <c r="I22" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
@@ -10561,16 +10791,18 @@
       <c r="Q22" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R22" s="6"/>
+      <c r="R22" s="6" t="s">
+        <v>1036</v>
+      </c>
       <c r="S22" s="6"/>
       <c r="T22" s="6" t="str">
-        <f ca="1">IF($C22="","",IF($V22="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V22,ROW(INDIRECT("1:"&amp;LEN($V22))),1)))=LEN($V22)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V22)&lt;8,"Too short - "&amp;LEN($V22)&amp;" digits (min 8)",IF(LEN($V22)&gt;15,"Too long - "&amp;LEN($V22)&amp;" digits (max 15)",IF($H22="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H22,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H22,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H22&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H22&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V22,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H22,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H22,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H22,tblCountries[Name],0)),"0")&amp;" for "&amp;$H22,"OK"))))))))</f>
+        <f ca="1">IF($C22="",IF(SUMPRODUCT(LEN($A22:$S22))+LEN($U22)&gt;0,"Required - this field is missing",""),IF($V22="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V22,ROW(INDIRECT("1:"&amp;LEN($V22))),1)))=LEN($V22)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V22)&lt;8,"Too short - "&amp;LEN($V22)&amp;" digits (min 8)",IF(LEN($V22)&gt;15,"Too long - "&amp;LEN($V22)&amp;" digits (max 15)",IF($H22="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H22,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H22,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H22&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H22&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V22,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H22,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H22,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H22,tblCountries[Name],0)),"0")&amp;" for "&amp;$H22,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U22" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V22" s="11" t="str">
+      <c r="V22" s="6" t="str">
         <f t="shared" si="0"/>
         <v>36301234567</v>
       </c>
@@ -10600,20 +10832,22 @@
       </c>
       <c r="AC22" s="6"/>
       <c r="AD22" s="7" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>940</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="9" t="s">
         <v>941</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>942</v>
-      </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E23" s="9" t="s">
         <v>844</v>
       </c>
@@ -10624,7 +10858,9 @@
       <c r="H23" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="I23" s="6"/>
+      <c r="I23" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
@@ -10637,16 +10873,18 @@
       <c r="Q23" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R23" s="6"/>
+      <c r="R23" s="6" t="s">
+        <v>1037</v>
+      </c>
       <c r="S23" s="6"/>
       <c r="T23" s="6" t="str">
-        <f ca="1">IF($C23="","",IF($V23="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V23,ROW(INDIRECT("1:"&amp;LEN($V23))),1)))=LEN($V23)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V23)&lt;8,"Too short - "&amp;LEN($V23)&amp;" digits (min 8)",IF(LEN($V23)&gt;15,"Too long - "&amp;LEN($V23)&amp;" digits (max 15)",IF($H23="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H23,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H23,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H23&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H23&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V23,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H23,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H23,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H23,tblCountries[Name],0)),"0")&amp;" for "&amp;$H23,"OK"))))))))</f>
+        <f ca="1">IF($C23="",IF(SUMPRODUCT(LEN($A23:$S23))+LEN($U23)&gt;0,"Required - this field is missing",""),IF($V23="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V23,ROW(INDIRECT("1:"&amp;LEN($V23))),1)))=LEN($V23)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V23)&lt;8,"Too short - "&amp;LEN($V23)&amp;" digits (min 8)",IF(LEN($V23)&gt;15,"Too long - "&amp;LEN($V23)&amp;" digits (max 15)",IF($H23="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H23,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H23,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H23&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H23&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V23,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H23,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H23,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H23,tblCountries[Name],0)),"0")&amp;" for "&amp;$H23,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>943</v>
-      </c>
-      <c r="V23" s="11" t="str">
+        <v>942</v>
+      </c>
+      <c r="V23" s="6" t="str">
         <f t="shared" si="0"/>
         <v>971501234567</v>
       </c>
@@ -10676,20 +10914,22 @@
       </c>
       <c r="AC23" s="6"/>
       <c r="AD23" s="7" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>945</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="9" t="s">
         <v>946</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>947</v>
-      </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E24" s="9" t="s">
         <v>844</v>
       </c>
@@ -10700,7 +10940,9 @@
       <c r="H24" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="I24" s="6"/>
+      <c r="I24" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
@@ -10713,16 +10955,18 @@
       <c r="Q24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R24" s="6"/>
+      <c r="R24" s="6" t="s">
+        <v>1038</v>
+      </c>
       <c r="S24" s="6"/>
       <c r="T24" s="6" t="str">
-        <f ca="1">IF($C24="","",IF($V24="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V24,ROW(INDIRECT("1:"&amp;LEN($V24))),1)))=LEN($V24)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V24)&lt;8,"Too short - "&amp;LEN($V24)&amp;" digits (min 8)",IF(LEN($V24)&gt;15,"Too long - "&amp;LEN($V24)&amp;" digits (max 15)",IF($H24="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H24,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H24,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H24&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H24&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V24,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H24,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H24,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H24,tblCountries[Name],0)),"0")&amp;" for "&amp;$H24,"OK"))))))))</f>
+        <f ca="1">IF($C24="",IF(SUMPRODUCT(LEN($A24:$S24))+LEN($U24)&gt;0,"Required - this field is missing",""),IF($V24="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V24,ROW(INDIRECT("1:"&amp;LEN($V24))),1)))=LEN($V24)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V24)&lt;8,"Too short - "&amp;LEN($V24)&amp;" digits (min 8)",IF(LEN($V24)&gt;15,"Too long - "&amp;LEN($V24)&amp;" digits (max 15)",IF($H24="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H24,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H24,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H24&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H24&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V24,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H24,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H24,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H24,tblCountries[Name],0)),"0")&amp;" for "&amp;$H24,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>948</v>
-      </c>
-      <c r="V24" s="11" t="str">
+        <v>947</v>
+      </c>
+      <c r="V24" s="6" t="str">
         <f t="shared" si="0"/>
         <v>972501234567</v>
       </c>
@@ -10752,20 +10996,22 @@
       </c>
       <c r="AC24" s="6"/>
       <c r="AD24" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>950</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="9" t="s">
         <v>951</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>952</v>
-      </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E25" s="9" t="s">
         <v>844</v>
       </c>
@@ -10776,7 +11022,9 @@
       <c r="H25" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="I25" s="6"/>
+      <c r="I25" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
@@ -10789,16 +11037,18 @@
       <c r="Q25" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R25" s="6"/>
+      <c r="R25" s="6" t="s">
+        <v>1039</v>
+      </c>
       <c r="S25" s="6"/>
       <c r="T25" s="6" t="str">
-        <f ca="1">IF($C25="","",IF($V25="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V25,ROW(INDIRECT("1:"&amp;LEN($V25))),1)))=LEN($V25)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V25)&lt;8,"Too short - "&amp;LEN($V25)&amp;" digits (min 8)",IF(LEN($V25)&gt;15,"Too long - "&amp;LEN($V25)&amp;" digits (max 15)",IF($H25="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H25,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H25,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H25&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H25&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V25,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H25,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H25,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H25,tblCountries[Name],0)),"0")&amp;" for "&amp;$H25,"OK"))))))))</f>
+        <f ca="1">IF($C25="",IF(SUMPRODUCT(LEN($A25:$S25))+LEN($U25)&gt;0,"Required - this field is missing",""),IF($V25="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V25,ROW(INDIRECT("1:"&amp;LEN($V25))),1)))=LEN($V25)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V25)&lt;8,"Too short - "&amp;LEN($V25)&amp;" digits (min 8)",IF(LEN($V25)&gt;15,"Too long - "&amp;LEN($V25)&amp;" digits (max 15)",IF($H25="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H25,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H25,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H25&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H25&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V25,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H25,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H25,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H25,tblCountries[Name],0)),"0")&amp;" for "&amp;$H25,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U25" s="9" t="s">
-        <v>953</v>
-      </c>
-      <c r="V25" s="11" t="str">
+        <v>952</v>
+      </c>
+      <c r="V25" s="6" t="str">
         <f t="shared" si="0"/>
         <v>46701234567</v>
       </c>
@@ -10828,31 +11078,35 @@
       </c>
       <c r="AC25" s="6"/>
       <c r="AD25" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
+        <v>954</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>955</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="9" t="s">
         <v>956</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>957</v>
-      </c>
-      <c r="D26" s="6"/>
+      <c r="D26" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E26" s="9" t="s">
         <v>844</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="9" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="I26" s="6"/>
+      <c r="I26" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
@@ -10865,16 +11119,18 @@
       <c r="Q26" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R26" s="6"/>
+      <c r="R26" s="6" t="s">
+        <v>1040</v>
+      </c>
       <c r="S26" s="6"/>
       <c r="T26" s="6" t="str">
-        <f ca="1">IF($C26="","",IF($V26="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V26,ROW(INDIRECT("1:"&amp;LEN($V26))),1)))=LEN($V26)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V26)&lt;8,"Too short - "&amp;LEN($V26)&amp;" digits (min 8)",IF(LEN($V26)&gt;15,"Too long - "&amp;LEN($V26)&amp;" digits (max 15)",IF($H26="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H26,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H26,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H26&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H26&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V26,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H26,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H26,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H26,tblCountries[Name],0)),"0")&amp;" for "&amp;$H26,"OK"))))))))</f>
+        <f ca="1">IF($C26="",IF(SUMPRODUCT(LEN($A26:$S26))+LEN($U26)&gt;0,"Required - this field is missing",""),IF($V26="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V26,ROW(INDIRECT("1:"&amp;LEN($V26))),1)))=LEN($V26)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V26)&lt;8,"Too short - "&amp;LEN($V26)&amp;" digits (min 8)",IF(LEN($V26)&gt;15,"Too long - "&amp;LEN($V26)&amp;" digits (max 15)",IF($H26="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H26,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H26,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H26&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H26&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V26,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H26,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H26,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H26,tblCountries[Name],0)),"0")&amp;" for "&amp;$H26,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U26" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V26" s="11" t="str">
+      <c r="V26" s="6" t="str">
         <f t="shared" si="0"/>
         <v>4915112345678</v>
       </c>
@@ -10904,31 +11160,35 @@
       </c>
       <c r="AC26" s="6"/>
       <c r="AD26" s="7" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="9" t="s">
         <v>961</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>962</v>
-      </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E27" s="9" t="s">
         <v>844</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="9" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="I27" s="6"/>
+      <c r="I27" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
@@ -10941,16 +11201,18 @@
       <c r="Q27" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R27" s="6"/>
+      <c r="R27" s="6" t="s">
+        <v>1041</v>
+      </c>
       <c r="S27" s="6"/>
       <c r="T27" s="6" t="str">
-        <f ca="1">IF($C27="","",IF($V27="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V27,ROW(INDIRECT("1:"&amp;LEN($V27))),1)))=LEN($V27)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V27)&lt;8,"Too short - "&amp;LEN($V27)&amp;" digits (min 8)",IF(LEN($V27)&gt;15,"Too long - "&amp;LEN($V27)&amp;" digits (max 15)",IF($H27="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H27,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H27,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H27&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H27&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V27,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H27,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H27,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H27,tblCountries[Name],0)),"0")&amp;" for "&amp;$H27,"OK"))))))))</f>
+        <f ca="1">IF($C27="",IF(SUMPRODUCT(LEN($A27:$S27))+LEN($U27)&gt;0,"Required - this field is missing",""),IF($V27="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V27,ROW(INDIRECT("1:"&amp;LEN($V27))),1)))=LEN($V27)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V27)&lt;8,"Too short - "&amp;LEN($V27)&amp;" digits (min 8)",IF(LEN($V27)&gt;15,"Too long - "&amp;LEN($V27)&amp;" digits (max 15)",IF($H27="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H27,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H27,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H27&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H27&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V27,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H27,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H27,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H27,tblCountries[Name],0)),"0")&amp;" for "&amp;$H27,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U27" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V27" s="11" t="str">
+      <c r="V27" s="6" t="str">
         <f t="shared" si="0"/>
         <v>351912345679</v>
       </c>
@@ -10980,31 +11242,35 @@
       </c>
       <c r="AC27" s="6"/>
       <c r="AD27" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>965</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="C28" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>967</v>
-      </c>
-      <c r="D28" s="6"/>
+      <c r="D28" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E28" s="9" t="s">
         <v>844</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="9" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="I28" s="6"/>
+      <c r="I28" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
@@ -11017,16 +11283,18 @@
       <c r="Q28" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R28" s="6"/>
+      <c r="R28" s="6" t="s">
+        <v>1042</v>
+      </c>
       <c r="S28" s="6"/>
       <c r="T28" s="6" t="str">
-        <f ca="1">IF($C28="","",IF($V28="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V28,ROW(INDIRECT("1:"&amp;LEN($V28))),1)))=LEN($V28)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V28)&lt;8,"Too short - "&amp;LEN($V28)&amp;" digits (min 8)",IF(LEN($V28)&gt;15,"Too long - "&amp;LEN($V28)&amp;" digits (max 15)",IF($H28="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H28,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H28,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H28&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H28&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V28,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H28,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H28,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H28,tblCountries[Name],0)),"0")&amp;" for "&amp;$H28,"OK"))))))))</f>
+        <f ca="1">IF($C28="",IF(SUMPRODUCT(LEN($A28:$S28))+LEN($U28)&gt;0,"Required - this field is missing",""),IF($V28="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V28,ROW(INDIRECT("1:"&amp;LEN($V28))),1)))=LEN($V28)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V28)&lt;8,"Too short - "&amp;LEN($V28)&amp;" digits (min 8)",IF(LEN($V28)&gt;15,"Too long - "&amp;LEN($V28)&amp;" digits (max 15)",IF($H28="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H28,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H28,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H28&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H28&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V28,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H28,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H28,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H28,tblCountries[Name],0)),"0")&amp;" for "&amp;$H28,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U28" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V28" s="11" t="str">
+      <c r="V28" s="6" t="str">
         <f t="shared" si="0"/>
         <v>353871234567</v>
       </c>
@@ -11056,20 +11324,22 @@
       </c>
       <c r="AC28" s="6"/>
       <c r="AD28" s="7" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="9" t="s">
         <v>971</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>972</v>
-      </c>
-      <c r="D29" s="6"/>
+      <c r="D29" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E29" s="9" t="s">
         <v>844</v>
       </c>
@@ -11080,7 +11350,9 @@
       <c r="H29" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="I29" s="6"/>
+      <c r="I29" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
@@ -11093,16 +11365,18 @@
       <c r="Q29" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R29" s="6"/>
+      <c r="R29" s="6" t="s">
+        <v>1043</v>
+      </c>
       <c r="S29" s="6"/>
       <c r="T29" s="6" t="str">
-        <f ca="1">IF($C29="","",IF($V29="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V29,ROW(INDIRECT("1:"&amp;LEN($V29))),1)))=LEN($V29)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V29)&lt;8,"Too short - "&amp;LEN($V29)&amp;" digits (min 8)",IF(LEN($V29)&gt;15,"Too long - "&amp;LEN($V29)&amp;" digits (max 15)",IF($H29="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H29,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H29,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H29&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H29&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V29,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H29,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H29,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H29,tblCountries[Name],0)),"0")&amp;" for "&amp;$H29,"OK"))))))))</f>
+        <f ca="1">IF($C29="",IF(SUMPRODUCT(LEN($A29:$S29))+LEN($U29)&gt;0,"Required - this field is missing",""),IF($V29="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V29,ROW(INDIRECT("1:"&amp;LEN($V29))),1)))=LEN($V29)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V29)&lt;8,"Too short - "&amp;LEN($V29)&amp;" digits (min 8)",IF(LEN($V29)&gt;15,"Too long - "&amp;LEN($V29)&amp;" digits (max 15)",IF($H29="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H29,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H29,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H29&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H29&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V29,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H29,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H29,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H29,tblCountries[Name],0)),"0")&amp;" for "&amp;$H29,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U29" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V29" s="11" t="str">
+      <c r="V29" s="6" t="str">
         <f t="shared" si="0"/>
         <v>385911234567</v>
       </c>
@@ -11132,31 +11406,35 @@
       </c>
       <c r="AC29" s="6"/>
       <c r="AD29" s="7" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="9" t="s">
         <v>975</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>976</v>
-      </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E30" s="9" t="s">
         <v>844</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="9" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="I30" s="6"/>
+      <c r="I30" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
@@ -11169,16 +11447,18 @@
       <c r="Q30" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R30" s="6"/>
+      <c r="R30" s="6" t="s">
+        <v>1044</v>
+      </c>
       <c r="S30" s="6"/>
       <c r="T30" s="6" t="str">
-        <f ca="1">IF($C30="","",IF($V30="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V30,ROW(INDIRECT("1:"&amp;LEN($V30))),1)))=LEN($V30)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V30)&lt;8,"Too short - "&amp;LEN($V30)&amp;" digits (min 8)",IF(LEN($V30)&gt;15,"Too long - "&amp;LEN($V30)&amp;" digits (max 15)",IF($H30="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H30,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H30,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H30&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H30&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V30,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H30,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H30,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H30,tblCountries[Name],0)),"0")&amp;" for "&amp;$H30,"OK"))))))))</f>
+        <f ca="1">IF($C30="",IF(SUMPRODUCT(LEN($A30:$S30))+LEN($U30)&gt;0,"Required - this field is missing",""),IF($V30="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V30,ROW(INDIRECT("1:"&amp;LEN($V30))),1)))=LEN($V30)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V30)&lt;8,"Too short - "&amp;LEN($V30)&amp;" digits (min 8)",IF(LEN($V30)&gt;15,"Too long - "&amp;LEN($V30)&amp;" digits (max 15)",IF($H30="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H30,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H30,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H30&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H30&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V30,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H30,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H30,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H30,tblCountries[Name],0)),"0")&amp;" for "&amp;$H30,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U30" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V30" s="11" t="str">
+      <c r="V30" s="6" t="str">
         <f t="shared" si="0"/>
         <v>386401234567</v>
       </c>
@@ -11208,20 +11488,22 @@
       </c>
       <c r="AC30" s="6"/>
       <c r="AD30" s="7" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>979</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="9" t="s">
         <v>980</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>981</v>
-      </c>
-      <c r="D31" s="6"/>
+      <c r="D31" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E31" s="9" t="s">
         <v>844</v>
       </c>
@@ -11232,7 +11514,9 @@
       <c r="H31" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="I31" s="6"/>
+      <c r="I31" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
@@ -11240,21 +11524,23 @@
       <c r="N31" s="6"/>
       <c r="O31" s="6"/>
       <c r="P31" s="6" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R31" s="6"/>
+      <c r="R31" s="6" t="s">
+        <v>1045</v>
+      </c>
       <c r="S31" s="6"/>
       <c r="T31" s="6" t="str">
-        <f ca="1">IF($C31="","",IF($V31="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V31,ROW(INDIRECT("1:"&amp;LEN($V31))),1)))=LEN($V31)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V31)&lt;8,"Too short - "&amp;LEN($V31)&amp;" digits (min 8)",IF(LEN($V31)&gt;15,"Too long - "&amp;LEN($V31)&amp;" digits (max 15)",IF($H31="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H31,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H31,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H31&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H31&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V31,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H31,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H31,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H31,tblCountries[Name],0)),"0")&amp;" for "&amp;$H31,"OK"))))))))</f>
+        <f ca="1">IF($C31="",IF(SUMPRODUCT(LEN($A31:$S31))+LEN($U31)&gt;0,"Required - this field is missing",""),IF($V31="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V31,ROW(INDIRECT("1:"&amp;LEN($V31))),1)))=LEN($V31)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V31)&lt;8,"Too short - "&amp;LEN($V31)&amp;" digits (min 8)",IF(LEN($V31)&gt;15,"Too long - "&amp;LEN($V31)&amp;" digits (max 15)",IF($H31="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H31,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H31,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H31&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H31&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V31,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H31,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H31,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H31,tblCountries[Name],0)),"0")&amp;" for "&amp;$H31,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U31" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V31" s="11" t="str">
+      <c r="V31" s="6" t="str">
         <f t="shared" si="0"/>
         <v>4915112345679</v>
       </c>
@@ -11284,20 +11570,22 @@
       </c>
       <c r="AC31" s="6"/>
       <c r="AD31" s="7" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="9" t="s">
         <v>985</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>986</v>
-      </c>
-      <c r="D32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E32" s="9" t="s">
         <v>844</v>
       </c>
@@ -11308,7 +11596,9 @@
       <c r="H32" s="6" t="s">
         <v>696</v>
       </c>
-      <c r="I32" s="6"/>
+      <c r="I32" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
@@ -11316,21 +11606,23 @@
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
       <c r="P32" s="6" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="Q32" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R32" s="6"/>
+      <c r="R32" s="6" t="s">
+        <v>1046</v>
+      </c>
       <c r="S32" s="6"/>
       <c r="T32" s="6" t="str">
-        <f ca="1">IF($C32="","",IF($V32="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V32,ROW(INDIRECT("1:"&amp;LEN($V32))),1)))=LEN($V32)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V32)&lt;8,"Too short - "&amp;LEN($V32)&amp;" digits (min 8)",IF(LEN($V32)&gt;15,"Too long - "&amp;LEN($V32)&amp;" digits (max 15)",IF($H32="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H32,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H32,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H32&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H32&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V32,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H32,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H32,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H32,tblCountries[Name],0)),"0")&amp;" for "&amp;$H32,"OK"))))))))</f>
+        <f ca="1">IF($C32="",IF(SUMPRODUCT(LEN($A32:$S32))+LEN($U32)&gt;0,"Required - this field is missing",""),IF($V32="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V32,ROW(INDIRECT("1:"&amp;LEN($V32))),1)))=LEN($V32)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V32)&lt;8,"Too short - "&amp;LEN($V32)&amp;" digits (min 8)",IF(LEN($V32)&gt;15,"Too long - "&amp;LEN($V32)&amp;" digits (max 15)",IF($H32="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H32,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H32,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H32&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H32&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V32,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H32,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H32,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H32,tblCountries[Name],0)),"0")&amp;" for "&amp;$H32,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U32" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V32" s="11" t="str">
+      <c r="V32" s="6" t="str">
         <f t="shared" si="0"/>
         <v>34612345678</v>
       </c>
@@ -11360,20 +11652,22 @@
       </c>
       <c r="AC32" s="6"/>
       <c r="AD32" s="7" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
+        <v>988</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>989</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="C33" s="9" t="s">
         <v>990</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>991</v>
-      </c>
-      <c r="D33" s="6"/>
+      <c r="D33" s="6" t="s">
+        <v>1013</v>
+      </c>
       <c r="E33" s="9" t="s">
         <v>844</v>
       </c>
@@ -11384,7 +11678,9 @@
       <c r="H33" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I33" s="6"/>
+      <c r="I33" s="6" t="s">
+        <v>1014</v>
+      </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
@@ -11395,18 +11691,20 @@
         <v>59</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>992</v>
-      </c>
-      <c r="R33" s="6"/>
+        <v>991</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>1047</v>
+      </c>
       <c r="S33" s="6"/>
       <c r="T33" s="6" t="str">
-        <f ca="1">IF($C33="","",IF($V33="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V33,ROW(INDIRECT("1:"&amp;LEN($V33))),1)))=LEN($V33)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V33)&lt;8,"Too short - "&amp;LEN($V33)&amp;" digits (min 8)",IF(LEN($V33)&gt;15,"Too long - "&amp;LEN($V33)&amp;" digits (max 15)",IF($H33="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H33,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H33,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H33&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H33&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V33,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H33,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H33,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H33,tblCountries[Name],0)),"0")&amp;" for "&amp;$H33,"OK"))))))))</f>
+        <f ca="1">IF($C33="",IF(SUMPRODUCT(LEN($A33:$S33))+LEN($U33)&gt;0,"Required - this field is missing",""),IF($V33="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V33,ROW(INDIRECT("1:"&amp;LEN($V33))),1)))=LEN($V33)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V33)&lt;8,"Too short - "&amp;LEN($V33)&amp;" digits (min 8)",IF(LEN($V33)&gt;15,"Too long - "&amp;LEN($V33)&amp;" digits (max 15)",IF($H33="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H33,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H33,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H33&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H33&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V33,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H33,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H33,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H33,tblCountries[Name],0)),"0")&amp;" for "&amp;$H33,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U33" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V33" s="11" t="str">
+      <c r="V33" s="6" t="str">
         <f t="shared" si="0"/>
         <v>4531234567</v>
       </c>
@@ -11436,20 +11734,22 @@
       </c>
       <c r="AC33" s="6"/>
       <c r="AD33" s="7" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>994</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="C34" s="9" t="s">
         <v>995</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>996</v>
-      </c>
-      <c r="D34" s="6"/>
+      <c r="D34" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="E34" s="9" t="s">
         <v>844</v>
       </c>
@@ -11460,7 +11760,9 @@
       <c r="H34" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="I34" s="6"/>
+      <c r="I34" s="6" t="s">
+        <v>1017</v>
+      </c>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
@@ -11471,18 +11773,20 @@
         <v>59</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>997</v>
-      </c>
-      <c r="R34" s="6"/>
+        <v>996</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>1048</v>
+      </c>
       <c r="S34" s="6"/>
       <c r="T34" s="6" t="str">
-        <f ca="1">IF($C34="","",IF($V34="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V34,ROW(INDIRECT("1:"&amp;LEN($V34))),1)))=LEN($V34)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V34)&lt;8,"Too short - "&amp;LEN($V34)&amp;" digits (min 8)",IF(LEN($V34)&gt;15,"Too long - "&amp;LEN($V34)&amp;" digits (max 15)",IF($H34="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H34,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H34,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H34&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H34&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V34,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H34,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H34,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H34,tblCountries[Name],0)),"0")&amp;" for "&amp;$H34,"OK"))))))))</f>
+        <f ca="1">IF($C34="",IF(SUMPRODUCT(LEN($A34:$S34))+LEN($U34)&gt;0,"Required - this field is missing",""),IF($V34="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V34,ROW(INDIRECT("1:"&amp;LEN($V34))),1)))=LEN($V34)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V34)&lt;8,"Too short - "&amp;LEN($V34)&amp;" digits (min 8)",IF(LEN($V34)&gt;15,"Too long - "&amp;LEN($V34)&amp;" digits (max 15)",IF($H34="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H34,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H34,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H34&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H34&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V34,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H34,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H34,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H34,tblCountries[Name],0)),"0")&amp;" for "&amp;$H34,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U34" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V34" s="11" t="str">
+      <c r="V34" s="6" t="str">
         <f t="shared" si="0"/>
         <v>306901234567</v>
       </c>
@@ -11512,20 +11816,22 @@
       </c>
       <c r="AC34" s="6"/>
       <c r="AD34" s="7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>999</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="C35" s="9" t="s">
         <v>1000</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D35" s="6"/>
+      <c r="D35" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="E35" s="9">
         <v>8.9352012345678899E+18</v>
       </c>
@@ -11536,7 +11842,9 @@
       <c r="H35" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="I35" s="6"/>
+      <c r="I35" s="6" t="s">
+        <v>1011</v>
+      </c>
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
@@ -11549,16 +11857,18 @@
       <c r="Q35" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R35" s="6"/>
+      <c r="R35" s="6" t="s">
+        <v>1049</v>
+      </c>
       <c r="S35" s="6"/>
       <c r="T35" s="6" t="str">
-        <f ca="1">IF($C35="","",IF($V35="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V35,ROW(INDIRECT("1:"&amp;LEN($V35))),1)))=LEN($V35)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V35)&lt;8,"Too short - "&amp;LEN($V35)&amp;" digits (min 8)",IF(LEN($V35)&gt;15,"Too long - "&amp;LEN($V35)&amp;" digits (max 15)",IF($H35="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H35,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H35,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H35&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H35&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V35,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H35,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H35,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H35,tblCountries[Name],0)),"0")&amp;" for "&amp;$H35,"OK"))))))))</f>
+        <f ca="1">IF($C35="",IF(SUMPRODUCT(LEN($A35:$S35))+LEN($U35)&gt;0,"Required - this field is missing",""),IF($V35="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V35,ROW(INDIRECT("1:"&amp;LEN($V35))),1)))=LEN($V35)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V35)&lt;8,"Too short - "&amp;LEN($V35)&amp;" digits (min 8)",IF(LEN($V35)&gt;15,"Too long - "&amp;LEN($V35)&amp;" digits (max 15)",IF($H35="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H35,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H35,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H35&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H35&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V35,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H35,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H35,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H35,tblCountries[Name],0)),"0")&amp;" for "&amp;$H35,"OK"))))))))</f>
         <v>OK</v>
       </c>
       <c r="U35" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="V35" s="11" t="str">
+      <c r="V35" s="6" t="str">
         <f t="shared" si="0"/>
         <v>380501234567</v>
       </c>
@@ -11588,156 +11898,215 @@
       </c>
       <c r="AC35" s="6"/>
       <c r="AD35" s="7" t="s">
-        <v>1002</v>
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6" t="str">
+        <f ca="1">IF($C36="",IF(SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0,"Required - this field is missing",""),IF($V36="","No digits at all - enter a phone number",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID($V36,ROW(INDIRECT("1:"&amp;LEN($V36))),1)))=LEN($V36)),"Digits only - no letters or symbols (+ ( ) - . and spaces are tolerated)",IF(LEN($V36)&lt;8,"Too short - "&amp;LEN($V36)&amp;" digits (min 8)",IF(LEN($V36)&gt;15,"Too long - "&amp;LEN($V36)&amp;" digits (max 15)",IF($H36="","WARNING: SIM_Country is empty - cannot check the country code",IF(ISNA(MATCH($H36,tblCountries[Name],0)),IF(ISNA(MATCH(TRIM(SUBSTITUTE($H36,CHAR(160)," ")),tblCountries[Name],0)),"WARNING: SIM_Country """&amp;$H36&amp;""" is not in tblCountries","WARNING: SIM_Country """&amp;$H36&amp;""" has stray spaces around it (usually from a paste) - retype it or pick it from the dropdown"),IF(LEFT($V36,LEN(TEXT(INDEX(tblCountries[DialCode],MATCH($H36,tblCountries[Name],0)),"0")))&lt;&gt;TEXT(INDEX(tblCountries[DialCode],MATCH($H36,tblCountries[Name],0)),"0"),"Wrong country code - must start with +"&amp;TEXT(INDEX(tblCountries[DialCode],MATCH($H36,tblCountries[Name],0)),"0")&amp;" for "&amp;$H36,"OK"))))))))</f>
+        <v>Required - this field is missing</v>
+      </c>
+      <c r="V36" s="11" t="str">
+        <f>IF($C36="","",IF(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C36&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),""),2)="00",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C36&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),""),3,255),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM($C36&amp;""),"+","")," ",""),"-",""),"(",""),")",""),".",""),CHAR(160),"")))</f>
+        <v/>
+      </c>
+      <c r="W36" s="6" t="str">
+        <f ca="1">IF($E36="",IF(SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0,"Required - this field is missing",""),IF(ISNUMBER($E36),"Stored as a NUMBER - every digit past the 15th is already lost. Format the column as Text and re-enter.",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID(TRIM($E36&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E36&amp;"")))),1)))=LEN(TRIM($E36&amp;""))),"Digits only - no +, -, spaces or any other character",IF(LEFT(TRIM($E36&amp;""),2)&lt;&gt;"89","Must start with 89 (ITU-T E.118 telecom prefix)",IF(LEN(TRIM($E36&amp;""))&lt;18,"Too short - "&amp;LEN(TRIM($E36&amp;""))&amp;" digits (min 18)",IF(LEN(TRIM($E36&amp;""))&gt;22,"Too long - "&amp;LEN(TRIM($E36&amp;""))&amp;" digits (max 22)",IF(NOT(MOD(SUMPRODUCT(MID(TRIM($E36&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E36&amp;"")))),1)*1*(1+MOD(LEN(TRIM($E36&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E36&amp;"")))),2))-MOD(LEN(TRIM($E36&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($E36&amp;"")))),2)*9*(MID(TRIM($E36&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($E36&amp;"")))),1)*1*2&gt;9)),10)=0),"WARNING: Luhn check digit does not match - likely a typo or a transposition","OK")))))))</f>
+        <v>Required - this field is missing</v>
+      </c>
+      <c r="X36" s="6" t="str">
+        <f ca="1">IF($U36="","",IF(NOT(SUMPRODUCT(--ISNUMBER(--MID(TRIM($U36&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($U36&amp;"")))),1)))=LEN(TRIM($U36&amp;""))),"Digits only - no +, -, spaces or any other character",IF(LEN(TRIM($U36&amp;""))&lt;&gt;15,"Must be exactly 15 digits - this one has "&amp;LEN(TRIM($U36&amp;"")),IF(NOT(MOD(SUMPRODUCT(MID(TRIM($U36&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($U36&amp;"")))),1)*1*(1+MOD(LEN(TRIM($U36&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($U36&amp;"")))),2))-MOD(LEN(TRIM($U36&amp;""))-ROW(INDIRECT("1:"&amp;LEN(TRIM($U36&amp;"")))),2)*9*(MID(TRIM($U36&amp;""),ROW(INDIRECT("1:"&amp;LEN(TRIM($U36&amp;"")))),1)*1*2&gt;9)),10)=0),"WARNING: Luhn check digit does not match - likely a typo or a transposition","OK"))))</f>
+        <v/>
+      </c>
+      <c r="Y36" s="6" t="str">
+        <f ca="1">IF($G36="","",IF(ISNUMBER($G36),IF(OR($G36&lt;DATE(2000,1,1),$G36&gt;TODAY()+730),"WARNING: real date, but outside 2000-01-01 .. today+2y - check the day/month order","OK"),IF(LEN(TRIM($G36&amp;""))&lt;&gt;10,"Must be dd-mm-yyyy - 10 characters, this one has "&amp;LEN(TRIM($G36&amp;"")),IF(AND(NOT(ISERROR(FIND(MID(TRIM($G36&amp;""),5,1),"-/."))),NOT(ISERROR(FIND(MID(TRIM($G36&amp;""),8,1),"-/."))),SUMPRODUCT(--ISNUMBER(--MID(LEFT(TRIM($G36&amp;""),4),ROW(INDIRECT("1:"&amp;LEN(LEFT(TRIM($G36&amp;""),4)))),1)))=LEN(LEFT(TRIM($G36&amp;""),4))),"Looks like yyyy-mm-dd - StartDate must put the DAY first: dd-mm-yyyy",IF(OR(MID(TRIM($G36&amp;""),3,1)&lt;&gt;MID(TRIM($G36&amp;""),6,1),ISERROR(FIND(MID(TRIM($G36&amp;""),3,1),"-/."))),"Separators must be in positions 3 and 6, matching, and be - or / or .",IF(NOT(AND(SUMPRODUCT(--ISNUMBER(--MID(LEFT(TRIM($G36&amp;""),2),ROW(INDIRECT("1:"&amp;LEN(LEFT(TRIM($G36&amp;""),2)))),1)))=LEN(LEFT(TRIM($G36&amp;""),2)),SUMPRODUCT(--ISNUMBER(--MID(MID(TRIM($G36&amp;""),4,2),ROW(INDIRECT("1:"&amp;LEN(MID(TRIM($G36&amp;""),4,2)))),1)))=LEN(MID(TRIM($G36&amp;""),4,2)),SUMPRODUCT(--ISNUMBER(--MID(RIGHT(TRIM($G36&amp;""),4),ROW(INDIRECT("1:"&amp;LEN(RIGHT(TRIM($G36&amp;""),4)))),1)))=LEN(RIGHT(TRIM($G36&amp;""),4)))),"Day, month and year must all be digits",IF(OR(LEFT(TRIM($G36&amp;""),2)*1&lt;1,LEFT(TRIM($G36&amp;""),2)*1&gt;31),"Day out of range - dd-mm-yyyy puts the DAY first",IF(OR(MID(TRIM($G36&amp;""),4,2)*1&lt;1,MID(TRIM($G36&amp;""),4,2)*1&gt;12),"Month out of range - dd-mm-yyyy puts the MONTH second",IF(OR(RIGHT(TRIM($G36&amp;""),4)*1&lt;2000,RIGHT(TRIM($G36&amp;""),4)*1&gt;2100),"Year out of range (2000-2100)",IF(DAY(DATE(RIGHT(TRIM($G36&amp;""),4)*1,MID(TRIM($G36&amp;""),4,2)*1,LEFT(TRIM($G36&amp;""),2)*1))&lt;&gt;LEFT(TRIM($G36&amp;""),2)*1,"Not a real calendar date (e.g. 31-02 or 30-02)","OK"))))))))))</f>
+        <v>OK</v>
+      </c>
+      <c r="Z36" s="6" t="str">
+        <f>IF($P36="","",IF(SUMPRODUCT(--EXACT($P36,Config!$G$2:$G$4))&gt;0,"OK",IF(NOT(ISNA(MATCH($P36,Config!$G$2:$G$4,0))),"WARNING: wrong capitalisation - should be """&amp;INDEX(Config!$G$2:$G$4,MATCH($P36,Config!$G$2:$G$4,0))&amp;""" exactly","Must be one of: Active, Deactivated, Suspended")))</f>
+        <v>OK</v>
+      </c>
+      <c r="AA36" s="6" t="str">
+        <f>IF($Q36="","",IF(SUMPRODUCT(--EXACT($Q36,Config!$H$2:$H$3))&gt;0,"OK",IF(NOT(ISNA(MATCH($Q36,Config!$H$2:$H$3,0))),"WARNING: wrong capitalisation - should be """&amp;INDEX(Config!$H$2:$H$3,MATCH($Q36,Config!$H$2:$H$3,0))&amp;""" exactly","Must be one of: eSIM, Physical SIM")))</f>
+        <v>OK</v>
+      </c>
+      <c r="AB36" s="6" t="str">
+        <f ca="1">IF(IF(OR($T36="",$T36="OK"),"","PhoneNr: "&amp;$T36&amp;"  //  ")&amp;IF(OR($W36="",$W36="OK"),"","ICC_ID: "&amp;$W36&amp;"  //  ")&amp;IF(OR($Y36="",$Y36="OK"),"","StartDate: "&amp;$Y36&amp;"  //  ")&amp;IF(OR($Z36="",$Z36="OK"),"","Status: "&amp;$Z36&amp;"  //  ")&amp;IF(OR($AA36="",$AA36="OK"),"","SIM Type: "&amp;$AA36&amp;"  //  ")&amp;IF(OR($X36="",$X36="OK"),"","IMEI: "&amp;$X36&amp;"  //  ")&amp;IF(AND(TRIM($H36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Email: Required - this field is missing  //  ","")="","OK",LEFT(IF(OR($T36="",$T36="OK"),"","PhoneNr: "&amp;$T36&amp;"  //  ")&amp;IF(OR($W36="",$W36="OK"),"","ICC_ID: "&amp;$W36&amp;"  //  ")&amp;IF(OR($Y36="",$Y36="OK"),"","StartDate: "&amp;$Y36&amp;"  //  ")&amp;IF(OR($Z36="",$Z36="OK"),"","Status: "&amp;$Z36&amp;"  //  ")&amp;IF(OR($AA36="",$AA36="OK"),"","SIM Type: "&amp;$AA36&amp;"  //  ")&amp;IF(OR($X36="",$X36="OK"),"","IMEI: "&amp;$X36&amp;"  //  ")&amp;IF(AND(TRIM($H36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Email: Required - this field is missing  //  ",""),LEN(IF(OR($T36="",$T36="OK"),"","PhoneNr: "&amp;$T36&amp;"  //  ")&amp;IF(OR($W36="",$W36="OK"),"","ICC_ID: "&amp;$W36&amp;"  //  ")&amp;IF(OR($Y36="",$Y36="OK"),"","StartDate: "&amp;$Y36&amp;"  //  ")&amp;IF(OR($Z36="",$Z36="OK"),"","Status: "&amp;$Z36&amp;"  //  ")&amp;IF(OR($AA36="",$AA36="OK"),"","SIM Type: "&amp;$AA36&amp;"  //  ")&amp;IF(OR($X36="",$X36="OK"),"","IMEI: "&amp;$X36&amp;"  //  ")&amp;IF(AND(TRIM($H36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"SIM_Country: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($I36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Provider: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($D36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Plan: Required - this field is missing  //  ","")&amp;IF(AND(TRIM($R36&amp;"")="",SUMPRODUCT(LEN($A36:$S36))+LEN($U36)&gt;0),"Email: Required - this field is missing  //  ",""))-6))</f>
+        <v>PhoneNr: Required - this field is missing  //  ICC_ID: Required - this field is missing  //  SIM_Country: Required - this field is missing  //  Provider: Required - this field is missing  //  Plan: Required - this field is missing  //  Email: Required - this field is missing</v>
+      </c>
+      <c r="AD36" s="7" t="s">
+        <v>1052</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C1048576">
-    <cfRule type="expression" dxfId="40" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="9" stopIfTrue="1">
+      <formula>LEFT($T2,8)="Required"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="10" stopIfTrue="1">
       <formula>AND($C2&lt;&gt;"", LEFT($T2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="11" stopIfTrue="1">
       <formula>AND($C2&lt;&gt;"", $T2&lt;&gt;"", $T2&lt;&gt;"OK", NOT(LEFT($T2,8)="WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="3">
+    <cfRule type="expression" dxfId="33" priority="12">
       <formula>$T2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E1048576">
-    <cfRule type="expression" dxfId="37" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="7" stopIfTrue="1">
+      <formula>LEFT($W2,8)="Required"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="16" stopIfTrue="1">
       <formula>AND($E2&lt;&gt;"", LEFT($W2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="17" stopIfTrue="1">
       <formula>AND($E2&lt;&gt;"", $W2&lt;&gt;"", $W2&lt;&gt;"OK", NOT(LEFT($W2,8)="WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="9">
+    <cfRule type="expression" dxfId="29" priority="18">
       <formula>$W2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G1048576">
-    <cfRule type="expression" dxfId="34" priority="13" stopIfTrue="1">
+  <conditionalFormatting sqref="G2:G1048576 Y2:Y1048576">
+    <cfRule type="expression" dxfId="28" priority="22" stopIfTrue="1">
       <formula>AND($G2&lt;&gt;"", LEFT($Y2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="23" stopIfTrue="1">
       <formula>AND($G2&lt;&gt;"", $Y2&lt;&gt;"", $Y2&lt;&gt;"OK", NOT(LEFT($Y2,8)="WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="15">
+    <cfRule type="expression" dxfId="26" priority="24">
       <formula>$Y2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H1048576">
-    <cfRule type="expression" dxfId="31" priority="40">
+    <cfRule type="expression" dxfId="25" priority="5" stopIfTrue="1">
+      <formula>AND(TRIM($H2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="49">
       <formula>AND($H2&lt;&gt;"",ISNA(MATCH($H2,CountryNames,0)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P1048576">
-    <cfRule type="expression" dxfId="30" priority="19" stopIfTrue="1">
+  <conditionalFormatting sqref="P2:P1048576 Z2:Z1048576">
+    <cfRule type="expression" dxfId="23" priority="28" stopIfTrue="1">
       <formula>AND($P2&lt;&gt;"", LEFT($Z2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="29" stopIfTrue="1">
       <formula>AND($P2&lt;&gt;"", $Z2&lt;&gt;"", $Z2&lt;&gt;"OK", NOT(LEFT($Z2,8)="WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="21">
+    <cfRule type="expression" dxfId="21" priority="30">
       <formula>$Z2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q1048576">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+  <conditionalFormatting sqref="Q2:Q1048576 AA2:AA1048576">
+    <cfRule type="expression" dxfId="20" priority="34" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;"", LEFT($AA2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="35" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;"", $AA2&lt;&gt;"", $AA2&lt;&gt;"OK", NOT(LEFT($AA2,8)="WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27">
+    <cfRule type="expression" dxfId="18" priority="36">
       <formula>$AA2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T1048576">
-    <cfRule type="expression" dxfId="24" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="13" stopIfTrue="1">
       <formula>AND($C2&lt;&gt;"", LEFT($T2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="14" stopIfTrue="1">
       <formula>AND($C2&lt;&gt;"", $T2&lt;&gt;"", $T2&lt;&gt;"OK", NOT(LEFT($T2,8)="WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="6">
+    <cfRule type="expression" dxfId="15" priority="15">
       <formula>$T2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U1048576">
-    <cfRule type="expression" dxfId="21" priority="31" stopIfTrue="1">
+  <conditionalFormatting sqref="U2:U1048576 X2:X1048576">
+    <cfRule type="expression" dxfId="14" priority="40" stopIfTrue="1">
       <formula>AND($U2&lt;&gt;"", LEFT($X2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="41" stopIfTrue="1">
       <formula>AND($U2&lt;&gt;"", $X2&lt;&gt;"", $X2&lt;&gt;"OK", NOT(LEFT($X2,8)="WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="33">
+    <cfRule type="expression" dxfId="12" priority="42">
       <formula>$X2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W1048576">
-    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="19" stopIfTrue="1">
       <formula>AND($E2&lt;&gt;"", LEFT($W2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="20" stopIfTrue="1">
       <formula>AND($E2&lt;&gt;"", $W2&lt;&gt;"", $W2&lt;&gt;"OK", NOT(LEFT($W2,8)="WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12">
+    <cfRule type="expression" dxfId="9" priority="21">
       <formula>$W2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X1048576">
-    <cfRule type="expression" dxfId="15" priority="34" stopIfTrue="1">
-      <formula>AND($U2&lt;&gt;"", LEFT($X2,8)="WARNING:")</formula>
+  <conditionalFormatting sqref="AB2:AB1048576">
+    <cfRule type="expression" dxfId="8" priority="46" stopIfTrue="1">
+      <formula>OR(AND($T2&lt;&gt;"",$T2&lt;&gt;"OK",LEFT($T2,8)&lt;&gt;"WARNING:"),AND($W2&lt;&gt;"",$W2&lt;&gt;"OK",LEFT($W2,8)&lt;&gt;"WARNING:"),AND($Y2&lt;&gt;"",$Y2&lt;&gt;"OK",LEFT($Y2,8)&lt;&gt;"WARNING:"),AND($Z2&lt;&gt;"",$Z2&lt;&gt;"OK",LEFT($Z2,8)&lt;&gt;"WARNING:"),AND($AA2&lt;&gt;"",$AA2&lt;&gt;"OK",LEFT($AA2,8)&lt;&gt;"WARNING:"),AND($X2&lt;&gt;"",$X2&lt;&gt;"OK",LEFT($X2,8)&lt;&gt;"WARNING:"))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="35" stopIfTrue="1">
-      <formula>AND($U2&lt;&gt;"", $X2&lt;&gt;"", $X2&lt;&gt;"OK", NOT(LEFT($X2,8)="WARNING:"))</formula>
+    <cfRule type="expression" dxfId="7" priority="47" stopIfTrue="1">
+      <formula>OR(LEFT($T2,8)="WARNING:",LEFT($W2,8)="WARNING:",LEFT($Y2,8)="WARNING:",LEFT($Z2,8)="WARNING:",LEFT($AA2,8)="WARNING:",LEFT($X2,8)="WARNING:")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="36">
-      <formula>$X2="OK"</formula>
+    <cfRule type="expression" dxfId="6" priority="48">
+      <formula>$AB2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y1048576">
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
-      <formula>AND($G2&lt;&gt;"", LEFT($Y2,8)="WARNING:")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="17" stopIfTrue="1">
-      <formula>AND($G2&lt;&gt;"", $Y2&lt;&gt;"", $Y2&lt;&gt;"OK", NOT(LEFT($Y2,8)="WARNING:"))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="18">
-      <formula>$Y2="OK"</formula>
+  <conditionalFormatting sqref="T2:T1048576">
+    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
+      <formula>LEFT($T2,8)="Required"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z1048576">
-    <cfRule type="expression" dxfId="9" priority="22" stopIfTrue="1">
-      <formula>AND($P2&lt;&gt;"", LEFT($Z2,8)="WARNING:")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="23" stopIfTrue="1">
-      <formula>AND($P2&lt;&gt;"", $Z2&lt;&gt;"", $Z2&lt;&gt;"OK", NOT(LEFT($Z2,8)="WARNING:"))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="24">
-      <formula>$Z2="OK"</formula>
+  <conditionalFormatting sqref="W2:W1048576">
+    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
+      <formula>LEFT($W2,8)="Required"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA1048576">
-    <cfRule type="expression" dxfId="6" priority="28" stopIfTrue="1">
-      <formula>AND($Q2&lt;&gt;"", LEFT($AA2,8)="WARNING:")</formula>
+  <conditionalFormatting sqref="I2:I1048576">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+      <formula>AND(TRIM($I2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="29" stopIfTrue="1">
-      <formula>AND($Q2&lt;&gt;"", $AA2&lt;&gt;"", $AA2&lt;&gt;"OK", NOT(LEFT($AA2,8)="WARNING:"))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D1048576">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+      <formula>AND(TRIM($D2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="30">
-      <formula>$AA2="OK"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R1048576">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>AND(TRIM($R2&amp;"")="",SUMPRODUCT(LEN($A2:$S2))+LEN($U2)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB1048576">
-    <cfRule type="expression" dxfId="3" priority="37" stopIfTrue="1">
-      <formula>OR(AND($T2&lt;&gt;"",$T2&lt;&gt;"OK",LEFT($T2,8)&lt;&gt;"WARNING:"),AND($W2&lt;&gt;"",$W2&lt;&gt;"OK",LEFT($W2,8)&lt;&gt;"WARNING:"),AND($Y2&lt;&gt;"",$Y2&lt;&gt;"OK",LEFT($Y2,8)&lt;&gt;"WARNING:"),AND($Z2&lt;&gt;"",$Z2&lt;&gt;"OK",LEFT($Z2,8)&lt;&gt;"WARNING:"),AND($AA2&lt;&gt;"",$AA2&lt;&gt;"OK",LEFT($AA2,8)&lt;&gt;"WARNING:"),AND($X2&lt;&gt;"",$X2&lt;&gt;"OK",LEFT($X2,8)&lt;&gt;"WARNING:"))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="38" stopIfTrue="1">
-      <formula>OR(LEFT($T2,8)="WARNING:",LEFT($W2,8)="WARNING:",LEFT($Y2,8)="WARNING:",LEFT($Z2,8)="WARNING:",LEFT($AA2,8)="WARNING:",LEFT($X2,8)="WARNING:")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="39">
-      <formula>$AB2="OK"</formula>
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("Required - this field is missing",$AB2))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
